--- a/Data/4DataSet_woPG.xlsx
+++ b/Data/4DataSet_woPG.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\survey-outer\第二篇开头\论文2\数据整理\OT_QCM2Net\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niu\Documents\Codex\2026-07-14\7-30-slack-plugin-slack-openai-4\outputs\VLM_DTI_FinalProvenance_20260723\VLM-DTI source code\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0220988-FF70-4304-A2F9-D6E44CA8E155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3C81D6A-279F-4A0B-9475-E07DBDABCB53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30" yWindow="285" windowWidth="16350" windowHeight="14685" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7620" yWindow="825" windowWidth="16350" windowHeight="14415" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="celegans" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="19">
   <si>
     <t>Dataset</t>
   </si>
@@ -48,9 +48,6 @@
   </si>
   <si>
     <t>Seed</t>
-  </si>
-  <si>
-    <t>BestEpoch</t>
   </si>
   <si>
     <t>AUC_Test</t>
@@ -1486,13 +1483,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1523,22 +1520,19 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="C2" s="1">
         <v>42</v>
       </c>
       <c r="D2" s="4">
-        <v>15</v>
+        <v>0.99390000000000001</v>
       </c>
       <c r="E2" s="4">
         <v>0.99390000000000001</v>
@@ -1547,138 +1541,126 @@
         <v>0.99390000000000001</v>
       </c>
       <c r="G2" s="4">
-        <v>0.99390000000000001</v>
+        <v>0.97309999999999997</v>
       </c>
       <c r="H2" s="4">
-        <v>0.97309999999999997</v>
+        <v>0.96530000000000005</v>
       </c>
       <c r="I2" s="4">
-        <v>0.96530000000000005</v>
+        <v>0.97050000000000003</v>
       </c>
       <c r="J2" s="4">
-        <v>0.97050000000000003</v>
-      </c>
-      <c r="K2" s="4">
         <v>0.96919999999999995</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="C3" s="1">
         <v>1234</v>
       </c>
       <c r="D3" s="4">
-        <v>16</v>
+        <v>0.99390000000000001</v>
       </c>
       <c r="E3" s="4">
-        <v>0.99390000000000001</v>
+        <v>0.99309999999999998</v>
       </c>
       <c r="F3" s="4">
         <v>0.99309999999999998</v>
       </c>
       <c r="G3" s="4">
-        <v>0.99309999999999998</v>
+        <v>0.96040000000000003</v>
       </c>
       <c r="H3" s="4">
-        <v>0.96040000000000003</v>
+        <v>0.97070000000000001</v>
       </c>
       <c r="I3" s="4">
-        <v>0.97070000000000001</v>
+        <v>0.96660000000000001</v>
       </c>
       <c r="J3" s="4">
-        <v>0.96660000000000001</v>
-      </c>
-      <c r="K3" s="4">
         <v>0.96550000000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="C4" s="1">
         <v>2025</v>
       </c>
       <c r="D4" s="4">
-        <v>29</v>
+        <v>0.99480000000000002</v>
       </c>
       <c r="E4" s="4">
-        <v>0.99480000000000002</v>
+        <v>0.99429999999999996</v>
       </c>
       <c r="F4" s="4">
         <v>0.99429999999999996</v>
       </c>
       <c r="G4" s="4">
-        <v>0.99429999999999996</v>
+        <v>0.95340000000000003</v>
       </c>
       <c r="H4" s="4">
-        <v>0.95340000000000003</v>
+        <v>0.98129999999999995</v>
       </c>
       <c r="I4" s="4">
-        <v>0.98129999999999995</v>
+        <v>0.96789999999999998</v>
       </c>
       <c r="J4" s="4">
-        <v>0.96789999999999998</v>
-      </c>
-      <c r="K4" s="4">
         <v>0.96709999999999996</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="C5" s="1">
         <v>12345</v>
       </c>
       <c r="D5" s="4">
-        <v>23</v>
+        <v>0.99480000000000002</v>
       </c>
       <c r="E5" s="4">
-        <v>0.99480000000000002</v>
+        <v>0.99460000000000004</v>
       </c>
       <c r="F5" s="4">
         <v>0.99460000000000004</v>
       </c>
       <c r="G5" s="4">
-        <v>0.99460000000000004</v>
+        <v>0.97319999999999995</v>
       </c>
       <c r="H5" s="4">
-        <v>0.97319999999999995</v>
+        <v>0.96799999999999997</v>
       </c>
       <c r="I5" s="4">
-        <v>0.96799999999999997</v>
+        <v>0.9718</v>
       </c>
       <c r="J5" s="4">
-        <v>0.9718</v>
-      </c>
-      <c r="K5" s="4">
         <v>0.97060000000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="C6" s="1">
         <v>666</v>
       </c>
       <c r="D6" s="4">
-        <v>12</v>
+        <v>0.99150000000000005</v>
       </c>
       <c r="E6" s="4">
         <v>0.99150000000000005</v>
@@ -1687,764 +1669,706 @@
         <v>0.99150000000000005</v>
       </c>
       <c r="G6" s="4">
-        <v>0.99150000000000005</v>
+        <v>0.95789999999999997</v>
       </c>
       <c r="H6" s="4">
-        <v>0.95789999999999997</v>
+        <v>0.97070000000000001</v>
       </c>
       <c r="I6" s="4">
-        <v>0.97070000000000001</v>
+        <v>0.96530000000000005</v>
       </c>
       <c r="J6" s="4">
-        <v>0.96530000000000005</v>
-      </c>
-      <c r="K6" s="4">
         <v>0.96419999999999995</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
+      <c r="D7" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D2:D6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D2:D6),"0.0000")</f>
+        <v>0.9938±0.0014</v>
+      </c>
       <c r="E7" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E2:E6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E2:E6),"0.0000")</f>
-        <v>0.9938±0.0014</v>
+        <f t="shared" ref="E7:J7" si="0" xml:space="preserve"> TEXT(AVERAGE(E2:E6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E2:E6),"0.0000")</f>
+        <v>0.9935±0.0012</v>
       </c>
       <c r="F7" t="str">
-        <f t="shared" ref="F7:K7" si="0" xml:space="preserve"> TEXT(AVERAGE(F2:F6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F2:F6),"0.0000")</f>
+        <f t="shared" si="0"/>
         <v>0.9935±0.0012</v>
       </c>
       <c r="G7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9935±0.0012</v>
+        <v>0.9636±0.0091</v>
       </c>
       <c r="H7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9636±0.0091</v>
+        <v>0.9712±0.0061</v>
       </c>
       <c r="I7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9712±0.0061</v>
+        <v>0.9684±0.0027</v>
       </c>
       <c r="J7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9684±0.0027</v>
-      </c>
-      <c r="K7" t="str">
-        <f t="shared" si="0"/>
         <v>0.9673±0.0026</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1">
         <v>42</v>
       </c>
       <c r="D8" s="4">
-        <v>28</v>
+        <v>0.96160000000000001</v>
       </c>
       <c r="E8" s="4">
-        <v>0.96160000000000001</v>
+        <v>0.9516</v>
       </c>
       <c r="F8" s="4">
-        <v>0.9516</v>
+        <v>0.95169999999999999</v>
       </c>
       <c r="G8" s="4">
-        <v>0.95169999999999999</v>
+        <v>0.87390000000000001</v>
       </c>
       <c r="H8" s="4">
-        <v>0.87390000000000001</v>
+        <v>0.86109999999999998</v>
       </c>
       <c r="I8" s="4">
-        <v>0.86109999999999998</v>
+        <v>0.8901</v>
       </c>
       <c r="J8" s="4">
-        <v>0.8901</v>
-      </c>
-      <c r="K8" s="4">
         <v>0.86739999999999995</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1">
         <v>1234</v>
       </c>
       <c r="D9" s="4">
-        <v>23</v>
+        <v>0.95409999999999995</v>
       </c>
       <c r="E9" s="4">
-        <v>0.95409999999999995</v>
+        <v>0.94210000000000005</v>
       </c>
       <c r="F9" s="4">
         <v>0.94210000000000005</v>
       </c>
       <c r="G9" s="4">
-        <v>0.94210000000000005</v>
+        <v>0.86650000000000005</v>
       </c>
       <c r="H9" s="4">
-        <v>0.86650000000000005</v>
+        <v>0.86109999999999998</v>
       </c>
       <c r="I9" s="4">
-        <v>0.86109999999999998</v>
+        <v>0.88649999999999995</v>
       </c>
       <c r="J9" s="4">
-        <v>0.88649999999999995</v>
-      </c>
-      <c r="K9" s="4">
         <v>0.86380000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="1">
         <v>2025</v>
       </c>
       <c r="D10" s="4">
-        <v>23</v>
+        <v>0.96160000000000001</v>
       </c>
       <c r="E10" s="4">
-        <v>0.96160000000000001</v>
+        <v>0.94989999999999997</v>
       </c>
       <c r="F10" s="4">
-        <v>0.94989999999999997</v>
+        <v>0.95</v>
       </c>
       <c r="G10" s="4">
-        <v>0.95</v>
+        <v>0.90180000000000005</v>
       </c>
       <c r="H10" s="4">
-        <v>0.90180000000000005</v>
+        <v>0.83160000000000001</v>
       </c>
       <c r="I10" s="4">
-        <v>0.83160000000000001</v>
+        <v>0.89180000000000004</v>
       </c>
       <c r="J10" s="4">
-        <v>0.89180000000000004</v>
-      </c>
-      <c r="K10" s="4">
         <v>0.86529999999999996</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="1">
         <v>12345</v>
       </c>
       <c r="D11" s="4">
-        <v>22</v>
+        <v>0.95740000000000003</v>
       </c>
       <c r="E11" s="4">
-        <v>0.95740000000000003</v>
+        <v>0.94179999999999997</v>
       </c>
       <c r="F11" s="4">
-        <v>0.94179999999999997</v>
+        <v>0.94189999999999996</v>
       </c>
       <c r="G11" s="4">
-        <v>0.94189999999999996</v>
+        <v>0.87829999999999997</v>
       </c>
       <c r="H11" s="4">
-        <v>0.87829999999999997</v>
+        <v>0.85050000000000003</v>
       </c>
       <c r="I11" s="4">
-        <v>0.85050000000000003</v>
+        <v>0.88829999999999998</v>
       </c>
       <c r="J11" s="4">
-        <v>0.88829999999999998</v>
-      </c>
-      <c r="K11" s="4">
         <v>0.86419999999999997</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" s="1">
         <v>666</v>
       </c>
       <c r="D12" s="4">
-        <v>18</v>
+        <v>0.93959999999999999</v>
       </c>
       <c r="E12" s="4">
-        <v>0.93959999999999999</v>
+        <v>0.92149999999999999</v>
       </c>
       <c r="F12" s="4">
-        <v>0.92149999999999999</v>
+        <v>0.92159999999999997</v>
       </c>
       <c r="G12" s="4">
-        <v>0.92159999999999997</v>
+        <v>0.86539999999999995</v>
       </c>
       <c r="H12" s="4">
-        <v>0.86539999999999995</v>
+        <v>0.85260000000000002</v>
       </c>
       <c r="I12" s="4">
-        <v>0.85260000000000002</v>
+        <v>0.88300000000000001</v>
       </c>
       <c r="J12" s="4">
-        <v>0.88300000000000001</v>
-      </c>
-      <c r="K12" s="4">
         <v>0.85899999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+      <c r="D13" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D8:D12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D8:D12),"0.0000")</f>
+        <v>0.9549±0.0091</v>
+      </c>
       <c r="E13" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E8:E12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E8:E12),"0.0000")</f>
-        <v>0.9549±0.0091</v>
+        <f t="shared" ref="E13:J13" si="1" xml:space="preserve"> TEXT(AVERAGE(E8:E12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E8:E12),"0.0000")</f>
+        <v>0.9414±0.0120</v>
       </c>
       <c r="F13" t="str">
-        <f t="shared" ref="F13:K13" si="1" xml:space="preserve"> TEXT(AVERAGE(F8:F12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F8:F12),"0.0000")</f>
-        <v>0.9414±0.0120</v>
+        <f t="shared" si="1"/>
+        <v>0.9415±0.0120</v>
       </c>
       <c r="G13" t="str">
         <f t="shared" si="1"/>
-        <v>0.9415±0.0120</v>
+        <v>0.8772±0.0148</v>
       </c>
       <c r="H13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8772±0.0148</v>
+        <v>0.8514±0.0121</v>
       </c>
       <c r="I13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8514±0.0121</v>
+        <v>0.8879±0.0034</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8879±0.0034</v>
-      </c>
-      <c r="K13" t="str">
-        <f t="shared" si="1"/>
         <v>0.8639±0.0031</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C14" s="1">
         <v>42</v>
       </c>
       <c r="D14" s="4">
-        <v>16</v>
+        <v>0.9536</v>
       </c>
       <c r="E14" s="4">
-        <v>0.9536</v>
+        <v>0.96679999999999999</v>
       </c>
       <c r="F14" s="4">
         <v>0.96679999999999999</v>
       </c>
       <c r="G14" s="4">
-        <v>0.96679999999999999</v>
+        <v>0.96830000000000005</v>
       </c>
       <c r="H14" s="4">
-        <v>0.96830000000000005</v>
+        <v>0.79459999999999997</v>
       </c>
       <c r="I14" s="4">
-        <v>0.79459999999999997</v>
+        <v>0.8679</v>
       </c>
       <c r="J14" s="4">
-        <v>0.8679</v>
-      </c>
-      <c r="K14" s="4">
         <v>0.87290000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" s="1">
         <v>1234</v>
       </c>
       <c r="D15" s="4">
-        <v>8</v>
+        <v>0.97019999999999995</v>
       </c>
       <c r="E15" s="4">
-        <v>0.97019999999999995</v>
+        <v>0.97640000000000005</v>
       </c>
       <c r="F15" s="4">
         <v>0.97640000000000005</v>
       </c>
       <c r="G15" s="4">
-        <v>0.97640000000000005</v>
+        <v>0.95660000000000001</v>
       </c>
       <c r="H15" s="4">
-        <v>0.95660000000000001</v>
+        <v>0.88100000000000001</v>
       </c>
       <c r="I15" s="4">
-        <v>0.88100000000000001</v>
+        <v>0.9093</v>
       </c>
       <c r="J15" s="4">
-        <v>0.9093</v>
-      </c>
-      <c r="K15" s="4">
         <v>0.9173</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C16" s="1">
         <v>2025</v>
       </c>
       <c r="D16" s="4">
-        <v>6</v>
+        <v>0.9637</v>
       </c>
       <c r="E16" s="4">
-        <v>0.9637</v>
+        <v>0.9728</v>
       </c>
       <c r="F16" s="4">
         <v>0.9728</v>
       </c>
       <c r="G16" s="4">
-        <v>0.9728</v>
+        <v>0.96779999999999999</v>
       </c>
       <c r="H16" s="4">
-        <v>0.96779999999999999</v>
+        <v>0.81040000000000001</v>
       </c>
       <c r="I16" s="4">
-        <v>0.81040000000000001</v>
+        <v>0.87639999999999996</v>
       </c>
       <c r="J16" s="4">
-        <v>0.87639999999999996</v>
-      </c>
-      <c r="K16" s="4">
         <v>0.8821</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C17" s="1">
         <v>12345</v>
       </c>
       <c r="D17" s="4">
-        <v>6</v>
+        <v>0.96599999999999997</v>
       </c>
       <c r="E17" s="4">
-        <v>0.96599999999999997</v>
+        <v>0.9738</v>
       </c>
       <c r="F17" s="4">
-        <v>0.9738</v>
+        <v>0.97389999999999999</v>
       </c>
       <c r="G17" s="4">
-        <v>0.97389999999999999</v>
+        <v>0.96919999999999995</v>
       </c>
       <c r="H17" s="4">
-        <v>0.96919999999999995</v>
+        <v>0.81779999999999997</v>
       </c>
       <c r="I17" s="4">
-        <v>0.81779999999999997</v>
+        <v>0.88119999999999998</v>
       </c>
       <c r="J17" s="4">
-        <v>0.88119999999999998</v>
-      </c>
-      <c r="K17" s="4">
         <v>0.8871</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C18" s="1">
         <v>666</v>
       </c>
       <c r="D18" s="4">
-        <v>7</v>
+        <v>0.97060000000000002</v>
       </c>
       <c r="E18" s="4">
-        <v>0.97060000000000002</v>
+        <v>0.97619999999999996</v>
       </c>
       <c r="F18" s="4">
         <v>0.97619999999999996</v>
       </c>
       <c r="G18" s="4">
-        <v>0.97619999999999996</v>
+        <v>0.96360000000000001</v>
       </c>
       <c r="H18" s="4">
-        <v>0.96360000000000001</v>
+        <v>0.88570000000000004</v>
       </c>
       <c r="I18" s="4">
-        <v>0.88570000000000004</v>
+        <v>0.91559999999999997</v>
       </c>
       <c r="J18" s="4">
-        <v>0.91559999999999997</v>
-      </c>
-      <c r="K18" s="4">
         <v>0.92300000000000004</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
+      <c r="D19" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D14:D18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D14:D18),"0.0000")</f>
+        <v>0.9648±0.0069</v>
+      </c>
       <c r="E19" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E14:E18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E14:E18),"0.0000")</f>
-        <v>0.9648±0.0069</v>
+        <f t="shared" ref="E19:J19" si="2" xml:space="preserve"> TEXT(AVERAGE(E14:E18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E14:E18),"0.0000")</f>
+        <v>0.9732±0.0039</v>
       </c>
       <c r="F19" t="str">
-        <f t="shared" ref="F19:K19" si="2" xml:space="preserve"> TEXT(AVERAGE(F14:F18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F14:F18),"0.0000")</f>
+        <f t="shared" si="2"/>
         <v>0.9732±0.0039</v>
       </c>
       <c r="G19" t="str">
         <f t="shared" si="2"/>
-        <v>0.9732±0.0039</v>
+        <v>0.9651±0.0052</v>
       </c>
       <c r="H19" t="str">
         <f t="shared" si="2"/>
-        <v>0.9651±0.0052</v>
+        <v>0.8379±0.0424</v>
       </c>
       <c r="I19" t="str">
         <f t="shared" si="2"/>
-        <v>0.8379±0.0424</v>
+        <v>0.8901±0.0211</v>
       </c>
       <c r="J19" t="str">
         <f t="shared" si="2"/>
-        <v>0.8901±0.0211</v>
-      </c>
-      <c r="K19" t="str">
-        <f t="shared" si="2"/>
         <v>0.8965±0.0223</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C20" s="1">
         <v>42</v>
       </c>
       <c r="D20" s="4">
-        <v>20</v>
+        <v>0.99690000000000001</v>
       </c>
       <c r="E20" s="4">
-        <v>0.99690000000000001</v>
+        <v>0.99719999999999998</v>
       </c>
       <c r="F20" s="4">
         <v>0.99719999999999998</v>
       </c>
       <c r="G20" s="4">
-        <v>0.99719999999999998</v>
+        <v>0.94810000000000005</v>
       </c>
       <c r="H20" s="4">
-        <v>0.94810000000000005</v>
+        <v>0.97989999999999999</v>
       </c>
       <c r="I20" s="4">
-        <v>0.97989999999999999</v>
+        <v>0.96230000000000004</v>
       </c>
       <c r="J20" s="4">
-        <v>0.96230000000000004</v>
-      </c>
-      <c r="K20" s="4">
         <v>0.9637</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C21" s="1">
         <v>1234</v>
       </c>
       <c r="D21" s="4">
-        <v>24</v>
+        <v>0.996</v>
       </c>
       <c r="E21" s="4">
-        <v>0.996</v>
+        <v>0.99660000000000004</v>
       </c>
       <c r="F21" s="4">
         <v>0.99660000000000004</v>
       </c>
       <c r="G21" s="4">
-        <v>0.99660000000000004</v>
+        <v>0.99319999999999997</v>
       </c>
       <c r="H21" s="4">
-        <v>0.99319999999999997</v>
+        <v>0.97319999999999995</v>
       </c>
       <c r="I21" s="4">
-        <v>0.97319999999999995</v>
+        <v>0.9829</v>
       </c>
       <c r="J21" s="4">
-        <v>0.9829</v>
-      </c>
-      <c r="K21" s="4">
         <v>0.98299999999999998</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C22" s="1">
         <v>2025</v>
       </c>
       <c r="D22" s="4">
-        <v>27</v>
+        <v>0.99639999999999995</v>
       </c>
       <c r="E22" s="4">
-        <v>0.99639999999999995</v>
+        <v>0.99680000000000002</v>
       </c>
       <c r="F22" s="4">
         <v>0.99680000000000002</v>
       </c>
       <c r="G22" s="4">
-        <v>0.99680000000000002</v>
+        <v>0.96</v>
       </c>
       <c r="H22" s="4">
-        <v>0.96</v>
+        <v>0.96640000000000004</v>
       </c>
       <c r="I22" s="4">
-        <v>0.96640000000000004</v>
+        <v>0.96230000000000004</v>
       </c>
       <c r="J22" s="4">
-        <v>0.96230000000000004</v>
-      </c>
-      <c r="K22" s="4">
         <v>0.96319999999999995</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C23" s="1">
         <v>12345</v>
       </c>
       <c r="D23" s="4">
-        <v>23</v>
+        <v>0.99680000000000002</v>
       </c>
       <c r="E23" s="4">
-        <v>0.99680000000000002</v>
+        <v>0.997</v>
       </c>
       <c r="F23" s="4">
         <v>0.997</v>
       </c>
       <c r="G23" s="4">
-        <v>0.997</v>
+        <v>0.96709999999999996</v>
       </c>
       <c r="H23" s="4">
-        <v>0.96709999999999996</v>
+        <v>0.98660000000000003</v>
       </c>
       <c r="I23" s="4">
-        <v>0.98660000000000003</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="J23" s="4">
-        <v>0.97599999999999998</v>
-      </c>
-      <c r="K23" s="4">
         <v>0.97670000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24" s="1">
         <v>666</v>
       </c>
       <c r="D24" s="4">
-        <v>28</v>
+        <v>0.99750000000000005</v>
       </c>
       <c r="E24" s="4">
-        <v>0.99750000000000005</v>
+        <v>0.99770000000000003</v>
       </c>
       <c r="F24" s="4">
         <v>0.99770000000000003</v>
       </c>
       <c r="G24" s="4">
-        <v>0.99770000000000003</v>
+        <v>0.95389999999999997</v>
       </c>
       <c r="H24" s="4">
-        <v>0.95389999999999997</v>
+        <v>0.97319999999999995</v>
       </c>
       <c r="I24" s="4">
-        <v>0.97319999999999995</v>
+        <v>0.96230000000000004</v>
       </c>
       <c r="J24" s="4">
-        <v>0.96230000000000004</v>
-      </c>
-      <c r="K24" s="4">
         <v>0.96350000000000002</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
+      <c r="D25" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D20:D24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D20:D24),"0.0000")</f>
+        <v>0.9967±0.0006</v>
+      </c>
       <c r="E25" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E20:E24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E20:E24),"0.0000")</f>
-        <v>0.9967±0.0006</v>
+        <f t="shared" ref="E25:J25" si="3" xml:space="preserve"> TEXT(AVERAGE(E20:E24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E20:E24),"0.0000")</f>
+        <v>0.9971±0.0004</v>
       </c>
       <c r="F25" t="str">
-        <f t="shared" ref="F25:K25" si="3" xml:space="preserve"> TEXT(AVERAGE(F20:F24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F20:F24),"0.0000")</f>
+        <f t="shared" si="3"/>
         <v>0.9971±0.0004</v>
       </c>
       <c r="G25" t="str">
         <f t="shared" si="3"/>
-        <v>0.9971±0.0004</v>
+        <v>0.9645±0.0176</v>
       </c>
       <c r="H25" t="str">
         <f t="shared" si="3"/>
-        <v>0.9645±0.0176</v>
+        <v>0.9759±0.0077</v>
       </c>
       <c r="I25" t="str">
         <f t="shared" si="3"/>
-        <v>0.9759±0.0077</v>
+        <v>0.9692±0.0097</v>
       </c>
       <c r="J25" t="str">
         <f t="shared" si="3"/>
-        <v>0.9692±0.0097</v>
-      </c>
-      <c r="K25" t="str">
-        <f t="shared" si="3"/>
         <v>0.9700±0.0092</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1">
         <v>42</v>
       </c>
       <c r="D26" s="4">
-        <v>24</v>
+        <v>0.99919999999999998</v>
       </c>
       <c r="E26" s="4">
-        <v>0.99919999999999998</v>
+        <v>0.99939999999999996</v>
       </c>
       <c r="F26" s="4">
         <v>0.99939999999999996</v>
       </c>
       <c r="G26" s="4">
-        <v>0.99939999999999996</v>
+        <v>0.99280000000000002</v>
       </c>
       <c r="H26" s="4">
         <v>0.99280000000000002</v>
       </c>
       <c r="I26" s="4">
+        <v>0.99199999999999999</v>
+      </c>
+      <c r="J26" s="4">
         <v>0.99280000000000002</v>
       </c>
-      <c r="J26" s="4">
-        <v>0.99199999999999999</v>
-      </c>
-      <c r="K26" s="4">
-        <v>0.99280000000000002</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C27" s="1">
         <v>1234</v>
       </c>
       <c r="D27" s="4">
-        <v>21</v>
+        <v>0.998</v>
       </c>
       <c r="E27" s="4">
-        <v>0.998</v>
+        <v>0.99819999999999998</v>
       </c>
       <c r="F27" s="4">
-        <v>0.99819999999999998</v>
+        <v>0.99829999999999997</v>
       </c>
       <c r="G27" s="4">
-        <v>0.99829999999999997</v>
+        <v>0.99260000000000004</v>
       </c>
       <c r="H27" s="4">
-        <v>0.99260000000000004</v>
+        <v>0.96399999999999997</v>
       </c>
       <c r="I27" s="4">
-        <v>0.96399999999999997</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="J27" s="4">
-        <v>0.97599999999999998</v>
-      </c>
-      <c r="K27" s="4">
         <v>0.97809999999999997</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C28" s="1">
         <v>2025</v>
       </c>
       <c r="D28" s="4">
-        <v>23</v>
+        <v>0.99460000000000004</v>
       </c>
       <c r="E28" s="4">
         <v>0.99460000000000004</v>
@@ -2453,117 +2377,108 @@
         <v>0.99460000000000004</v>
       </c>
       <c r="G28" s="4">
-        <v>0.99460000000000004</v>
+        <v>0.99250000000000005</v>
       </c>
       <c r="H28" s="4">
-        <v>0.99250000000000005</v>
+        <v>0.95679999999999998</v>
       </c>
       <c r="I28" s="4">
-        <v>0.95679999999999998</v>
+        <v>0.97199999999999998</v>
       </c>
       <c r="J28" s="4">
-        <v>0.97199999999999998</v>
-      </c>
-      <c r="K28" s="4">
         <v>0.97440000000000004</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C29" s="1">
         <v>12345</v>
       </c>
       <c r="D29" s="4">
-        <v>25</v>
+        <v>0.99829999999999997</v>
       </c>
       <c r="E29" s="4">
-        <v>0.99829999999999997</v>
+        <v>0.99870000000000003</v>
       </c>
       <c r="F29" s="4">
         <v>0.99870000000000003</v>
       </c>
       <c r="G29" s="4">
-        <v>0.99870000000000003</v>
+        <v>0.99250000000000005</v>
       </c>
       <c r="H29" s="4">
-        <v>0.99250000000000005</v>
+        <v>0.95679999999999998</v>
       </c>
       <c r="I29" s="4">
-        <v>0.95679999999999998</v>
+        <v>0.97199999999999998</v>
       </c>
       <c r="J29" s="4">
-        <v>0.97199999999999998</v>
-      </c>
-      <c r="K29" s="4">
         <v>0.97440000000000004</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C30" s="1">
         <v>666</v>
       </c>
       <c r="D30" s="4">
-        <v>28</v>
+        <v>0.99790000000000001</v>
       </c>
       <c r="E30" s="4">
-        <v>0.99790000000000001</v>
+        <v>0.99829999999999997</v>
       </c>
       <c r="F30" s="4">
         <v>0.99829999999999997</v>
       </c>
       <c r="G30" s="4">
-        <v>0.99829999999999997</v>
+        <v>0.99219999999999997</v>
       </c>
       <c r="H30" s="4">
-        <v>0.99219999999999997</v>
+        <v>0.91369999999999996</v>
       </c>
       <c r="I30" s="4">
-        <v>0.91369999999999996</v>
+        <v>0.94799999999999995</v>
       </c>
       <c r="J30" s="4">
-        <v>0.94799999999999995</v>
-      </c>
-      <c r="K30" s="4">
         <v>0.95130000000000003</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="D31" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D26:D30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D26:D30),"0.0000")</f>
+        <v>0.9976±0.0018</v>
+      </c>
       <c r="E31" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E26:E30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E26:E30),"0.0000")</f>
-        <v>0.9976±0.0018</v>
+        <f t="shared" ref="E31:J31" si="4" xml:space="preserve"> TEXT(AVERAGE(E26:E30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E26:E30),"0.0000")</f>
+        <v>0.9978±0.0019</v>
       </c>
       <c r="F31" t="str">
-        <f t="shared" ref="F31:K31" si="4" xml:space="preserve"> TEXT(AVERAGE(F26:F30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F26:F30),"0.0000")</f>
-        <v>0.9978±0.0019</v>
+        <f t="shared" si="4"/>
+        <v>0.9979±0.0019</v>
       </c>
       <c r="G31" t="str">
         <f t="shared" si="4"/>
-        <v>0.9979±0.0019</v>
+        <v>0.9925±0.0002</v>
       </c>
       <c r="H31" t="str">
         <f t="shared" si="4"/>
-        <v>0.9925±0.0002</v>
+        <v>0.9568±0.0283</v>
       </c>
       <c r="I31" t="str">
         <f t="shared" si="4"/>
-        <v>0.9568±0.0283</v>
+        <v>0.9720±0.0157</v>
       </c>
       <c r="J31" t="str">
-        <f t="shared" si="4"/>
-        <v>0.9720±0.0157</v>
-      </c>
-      <c r="K31" t="str">
         <f t="shared" si="4"/>
         <v>0.9742±0.0149</v>
       </c>
@@ -2577,10 +2492,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D4FE8A1-466E-4044-9083-70D3ABB3121B}">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2611,1047 +2526,965 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1">
         <v>42</v>
       </c>
       <c r="D2" s="4">
-        <v>11</v>
+        <v>0.98680000000000001</v>
       </c>
       <c r="E2" s="4">
-        <v>0.98680000000000001</v>
+        <v>0.99109999999999998</v>
       </c>
       <c r="F2" s="4">
         <v>0.99109999999999998</v>
       </c>
       <c r="G2" s="4">
-        <v>0.99109999999999998</v>
+        <v>0.98740000000000006</v>
       </c>
       <c r="H2" s="4">
-        <v>0.98740000000000006</v>
+        <v>0.89939999999999998</v>
       </c>
       <c r="I2" s="4">
-        <v>0.89939999999999998</v>
+        <v>0.94210000000000005</v>
       </c>
       <c r="J2" s="4">
-        <v>0.94210000000000005</v>
-      </c>
-      <c r="K2" s="4">
         <v>0.94130000000000003</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1">
         <v>1234</v>
       </c>
       <c r="D3" s="4">
-        <v>30</v>
+        <v>0.98680000000000001</v>
       </c>
       <c r="E3" s="4">
-        <v>0.98680000000000001</v>
+        <v>0.99099999999999999</v>
       </c>
       <c r="F3" s="4">
         <v>0.99099999999999999</v>
       </c>
       <c r="G3" s="4">
-        <v>0.99099999999999999</v>
+        <v>0.96030000000000004</v>
       </c>
       <c r="H3" s="4">
-        <v>0.96030000000000004</v>
+        <v>0.97409999999999997</v>
       </c>
       <c r="I3" s="4">
-        <v>0.97409999999999997</v>
+        <v>0.96579999999999999</v>
       </c>
       <c r="J3" s="4">
-        <v>0.96579999999999999</v>
-      </c>
-      <c r="K3" s="4">
         <v>0.96719999999999995</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1">
         <v>2025</v>
       </c>
       <c r="D4" s="4">
-        <v>13</v>
+        <v>0.98839999999999995</v>
       </c>
       <c r="E4" s="4">
-        <v>0.98839999999999995</v>
+        <v>0.99180000000000001</v>
       </c>
       <c r="F4" s="4">
         <v>0.99180000000000001</v>
       </c>
       <c r="G4" s="4">
-        <v>0.99180000000000001</v>
+        <v>0.99370000000000003</v>
       </c>
       <c r="H4" s="4">
-        <v>0.99370000000000003</v>
+        <v>0.91090000000000004</v>
       </c>
       <c r="I4" s="4">
-        <v>0.91090000000000004</v>
+        <v>0.95099999999999996</v>
       </c>
       <c r="J4" s="4">
-        <v>0.95099999999999996</v>
-      </c>
-      <c r="K4" s="4">
         <v>0.95050000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1">
         <v>12345</v>
       </c>
       <c r="D5" s="4">
-        <v>15</v>
+        <v>0.9879</v>
       </c>
       <c r="E5" s="4">
-        <v>0.9879</v>
+        <v>0.99129999999999996</v>
       </c>
       <c r="F5" s="4">
         <v>0.99129999999999996</v>
       </c>
       <c r="G5" s="4">
-        <v>0.99129999999999996</v>
+        <v>0.97299999999999998</v>
       </c>
       <c r="H5" s="4">
-        <v>0.97299999999999998</v>
+        <v>0.93100000000000005</v>
       </c>
       <c r="I5" s="4">
-        <v>0.93100000000000005</v>
+        <v>0.95099999999999996</v>
       </c>
       <c r="J5" s="4">
-        <v>0.95099999999999996</v>
-      </c>
-      <c r="K5" s="4">
         <v>0.95150000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" s="1">
         <v>666</v>
       </c>
       <c r="D6" s="4">
-        <v>19</v>
+        <v>0.98509999999999998</v>
       </c>
       <c r="E6" s="4">
-        <v>0.98509999999999998</v>
+        <v>0.98860000000000003</v>
       </c>
       <c r="F6" s="4">
         <v>0.98860000000000003</v>
       </c>
       <c r="G6" s="4">
-        <v>0.98860000000000003</v>
+        <v>0.96299999999999997</v>
       </c>
       <c r="H6" s="4">
-        <v>0.96299999999999997</v>
+        <v>0.97130000000000005</v>
       </c>
       <c r="I6" s="4">
-        <v>0.97130000000000005</v>
+        <v>0.96579999999999999</v>
       </c>
       <c r="J6" s="4">
-        <v>0.96579999999999999</v>
-      </c>
-      <c r="K6" s="4">
         <v>0.96709999999999996</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
+      <c r="D7" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D2:D6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D2:D6),"0.0000")</f>
+        <v>0.9870±0.0013</v>
+      </c>
       <c r="E7" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E2:E6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E2:E6),"0.0000")</f>
-        <v>0.9870±0.0013</v>
+        <f t="shared" ref="E7:J7" si="0" xml:space="preserve"> TEXT(AVERAGE(E2:E6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E2:E6),"0.0000")</f>
+        <v>0.9908±0.0012</v>
       </c>
       <c r="F7" t="str">
-        <f t="shared" ref="F7:K7" si="0" xml:space="preserve"> TEXT(AVERAGE(F2:F6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F2:F6),"0.0000")</f>
+        <f t="shared" si="0"/>
         <v>0.9908±0.0012</v>
       </c>
       <c r="G7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9908±0.0012</v>
+        <v>0.9755±0.0147</v>
       </c>
       <c r="H7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9755±0.0147</v>
+        <v>0.9373±0.0342</v>
       </c>
       <c r="I7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9373±0.0342</v>
+        <v>0.9551±0.0104</v>
       </c>
       <c r="J7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9551±0.0104</v>
-      </c>
-      <c r="K7" t="str">
-        <f t="shared" si="0"/>
         <v>0.9555±0.0113</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1">
         <v>42</v>
       </c>
       <c r="D8" s="4">
-        <v>22</v>
+        <v>0.92059999999999997</v>
       </c>
       <c r="E8" s="4">
-        <v>0.92059999999999997</v>
+        <v>0.90449999999999997</v>
       </c>
       <c r="F8" s="4">
-        <v>0.90449999999999997</v>
+        <v>0.90459999999999996</v>
       </c>
       <c r="G8" s="4">
-        <v>0.90459999999999996</v>
+        <v>0.8155</v>
       </c>
       <c r="H8" s="4">
-        <v>0.8155</v>
+        <v>0.81689999999999996</v>
       </c>
       <c r="I8" s="4">
-        <v>0.81689999999999996</v>
+        <v>0.83979999999999999</v>
       </c>
       <c r="J8" s="4">
-        <v>0.83979999999999999</v>
-      </c>
-      <c r="K8" s="4">
         <v>0.81620000000000004</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1">
         <v>1234</v>
       </c>
       <c r="D9" s="4">
-        <v>30</v>
+        <v>0.9274</v>
       </c>
       <c r="E9" s="4">
-        <v>0.9274</v>
+        <v>0.91259999999999997</v>
       </c>
       <c r="F9" s="4">
-        <v>0.91259999999999997</v>
+        <v>0.91269999999999996</v>
       </c>
       <c r="G9" s="4">
-        <v>0.91269999999999996</v>
+        <v>0.76890000000000003</v>
       </c>
       <c r="H9" s="4">
-        <v>0.76890000000000003</v>
+        <v>0.91359999999999997</v>
       </c>
       <c r="I9" s="4">
-        <v>0.91359999999999997</v>
+        <v>0.84289999999999998</v>
       </c>
       <c r="J9" s="4">
-        <v>0.84289999999999998</v>
-      </c>
-      <c r="K9" s="4">
         <v>0.83499999999999996</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="1">
         <v>2025</v>
       </c>
       <c r="D10" s="4">
-        <v>28</v>
+        <v>0.91769999999999996</v>
       </c>
       <c r="E10" s="4">
-        <v>0.91769999999999996</v>
+        <v>0.90529999999999999</v>
       </c>
       <c r="F10" s="4">
-        <v>0.90529999999999999</v>
+        <v>0.90539999999999998</v>
       </c>
       <c r="G10" s="4">
-        <v>0.90539999999999998</v>
+        <v>0.81389999999999996</v>
       </c>
       <c r="H10" s="4">
-        <v>0.81389999999999996</v>
+        <v>0.77029999999999998</v>
       </c>
       <c r="I10" s="4">
-        <v>0.77029999999999998</v>
+        <v>0.82330000000000003</v>
       </c>
       <c r="J10" s="4">
-        <v>0.82330000000000003</v>
-      </c>
-      <c r="K10" s="4">
         <v>0.79149999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="1">
         <v>12345</v>
       </c>
       <c r="D11" s="4">
-        <v>22</v>
+        <v>0.91749999999999998</v>
       </c>
       <c r="E11" s="4">
-        <v>0.91749999999999998</v>
+        <v>0.90400000000000003</v>
       </c>
       <c r="F11" s="4">
         <v>0.90400000000000003</v>
       </c>
       <c r="G11" s="4">
-        <v>0.90400000000000003</v>
+        <v>0.80989999999999995</v>
       </c>
       <c r="H11" s="4">
-        <v>0.80989999999999995</v>
+        <v>0.81689999999999996</v>
       </c>
       <c r="I11" s="4">
-        <v>0.81689999999999996</v>
+        <v>0.83679999999999999</v>
       </c>
       <c r="J11" s="4">
-        <v>0.83679999999999999</v>
-      </c>
-      <c r="K11" s="4">
         <v>0.81340000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" s="1">
         <v>666</v>
       </c>
       <c r="D12" s="4">
-        <v>15</v>
+        <v>0.90400000000000003</v>
       </c>
       <c r="E12" s="4">
-        <v>0.90400000000000003</v>
+        <v>0.89500000000000002</v>
       </c>
       <c r="F12" s="4">
-        <v>0.89500000000000002</v>
+        <v>0.89510000000000001</v>
       </c>
       <c r="G12" s="4">
-        <v>0.89510000000000001</v>
+        <v>0.81710000000000005</v>
       </c>
       <c r="H12" s="4">
-        <v>0.81710000000000005</v>
+        <v>0.72540000000000004</v>
       </c>
       <c r="I12" s="4">
-        <v>0.72540000000000004</v>
+        <v>0.80979999999999996</v>
       </c>
       <c r="J12" s="4">
-        <v>0.80979999999999996</v>
-      </c>
-      <c r="K12" s="4">
         <v>0.76849999999999996</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+      <c r="D13" t="str">
+        <f t="shared" ref="D13:J13" si="1" xml:space="preserve"> TEXT(AVERAGE(D8:D12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D8:D12),"0.0000")</f>
+        <v>0.9174±0.0085</v>
+      </c>
       <c r="E13" t="str">
-        <f t="shared" ref="E13:K13" si="1" xml:space="preserve"> TEXT(AVERAGE(E8:E12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E8:E12),"0.0000")</f>
-        <v>0.9174±0.0085</v>
+        <f t="shared" si="1"/>
+        <v>0.9043±0.0063</v>
       </c>
       <c r="F13" t="str">
         <f t="shared" si="1"/>
-        <v>0.9043±0.0063</v>
+        <v>0.9044±0.0063</v>
       </c>
       <c r="G13" t="str">
         <f t="shared" si="1"/>
-        <v>0.9044±0.0063</v>
+        <v>0.8051±0.0204</v>
       </c>
       <c r="H13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8051±0.0204</v>
+        <v>0.8086±0.0699</v>
       </c>
       <c r="I13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8086±0.0699</v>
+        <v>0.8305±0.0138</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8305±0.0138</v>
-      </c>
-      <c r="K13" t="str">
-        <f t="shared" si="1"/>
         <v>0.8049±0.0255</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C14" s="1">
         <v>42</v>
       </c>
       <c r="D14" s="4">
-        <v>30</v>
+        <v>0.97050000000000003</v>
       </c>
       <c r="E14" s="4">
-        <v>0.97050000000000003</v>
+        <v>0.95940000000000003</v>
       </c>
       <c r="F14" s="4">
         <v>0.95940000000000003</v>
       </c>
       <c r="G14" s="4">
-        <v>0.95940000000000003</v>
+        <v>0.9335</v>
       </c>
       <c r="H14" s="4">
-        <v>0.9335</v>
+        <v>0.88100000000000001</v>
       </c>
       <c r="I14" s="4">
-        <v>0.88100000000000001</v>
+        <v>0.92710000000000004</v>
       </c>
       <c r="J14" s="4">
-        <v>0.92710000000000004</v>
-      </c>
-      <c r="K14" s="4">
         <v>0.90649999999999997</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" s="1">
         <v>1234</v>
       </c>
       <c r="D15" s="4">
+        <v>0.97030000000000005</v>
+      </c>
+      <c r="E15" s="4">
+        <v>0.96319999999999995</v>
+      </c>
+      <c r="F15" s="4">
+        <v>0.96330000000000005</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0.96040000000000003</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.83979999999999999</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.92190000000000005</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.89610000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A16" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E15" s="4">
-        <v>0.97030000000000005</v>
-      </c>
-      <c r="F15" s="4">
-        <v>0.96319999999999995</v>
-      </c>
-      <c r="G15" s="4">
-        <v>0.96330000000000005</v>
-      </c>
-      <c r="H15" s="4">
-        <v>0.96040000000000003</v>
-      </c>
-      <c r="I15" s="4">
-        <v>0.83979999999999999</v>
-      </c>
-      <c r="J15" s="4">
-        <v>0.92190000000000005</v>
-      </c>
-      <c r="K15" s="4">
-        <v>0.89610000000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A16" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="B16" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C16" s="1">
         <v>2025</v>
       </c>
       <c r="D16" s="4">
-        <v>27</v>
+        <v>0.97330000000000005</v>
       </c>
       <c r="E16" s="4">
-        <v>0.97330000000000005</v>
+        <v>0.95820000000000005</v>
       </c>
       <c r="F16" s="4">
-        <v>0.95820000000000005</v>
+        <v>0.95830000000000004</v>
       </c>
       <c r="G16" s="4">
-        <v>0.95830000000000004</v>
+        <v>0.91049999999999998</v>
       </c>
       <c r="H16" s="4">
-        <v>0.91049999999999998</v>
+        <v>0.90259999999999996</v>
       </c>
       <c r="I16" s="4">
-        <v>0.90259999999999996</v>
+        <v>0.9254</v>
       </c>
       <c r="J16" s="4">
-        <v>0.9254</v>
-      </c>
-      <c r="K16" s="4">
         <v>0.90649999999999997</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A17" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C17" s="1">
         <v>12345</v>
       </c>
       <c r="D17" s="4">
-        <v>30</v>
+        <v>0.97189999999999999</v>
       </c>
       <c r="E17" s="4">
-        <v>0.97189999999999999</v>
+        <v>0.95730000000000004</v>
       </c>
       <c r="F17" s="4">
         <v>0.95730000000000004</v>
       </c>
       <c r="G17" s="4">
-        <v>0.95730000000000004</v>
+        <v>0.90229999999999999</v>
       </c>
       <c r="H17" s="4">
-        <v>0.90229999999999999</v>
+        <v>0.91990000000000005</v>
       </c>
       <c r="I17" s="4">
-        <v>0.91990000000000005</v>
+        <v>0.92800000000000005</v>
       </c>
       <c r="J17" s="4">
-        <v>0.92800000000000005</v>
-      </c>
-      <c r="K17" s="4">
         <v>0.91100000000000003</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A18" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C18" s="1">
         <v>666</v>
       </c>
       <c r="D18" s="4">
-        <v>12</v>
+        <v>0.97640000000000005</v>
       </c>
       <c r="E18" s="4">
-        <v>0.97640000000000005</v>
+        <v>0.96889999999999998</v>
       </c>
       <c r="F18" s="4">
-        <v>0.96889999999999998</v>
+        <v>0.96899999999999997</v>
       </c>
       <c r="G18" s="4">
-        <v>0.96899999999999997</v>
+        <v>0.94169999999999998</v>
       </c>
       <c r="H18" s="4">
-        <v>0.94169999999999998</v>
+        <v>0.87450000000000006</v>
       </c>
       <c r="I18" s="4">
-        <v>0.87450000000000006</v>
+        <v>0.92800000000000005</v>
       </c>
       <c r="J18" s="4">
-        <v>0.92800000000000005</v>
-      </c>
-      <c r="K18" s="4">
         <v>0.90680000000000005</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
+      <c r="D19" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D14:D18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D14:D18),"0.0000")</f>
+        <v>0.9725±0.0025</v>
+      </c>
       <c r="E19" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E14:E18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E14:E18),"0.0000")</f>
-        <v>0.9725±0.0025</v>
+        <f t="shared" ref="E19:J19" si="2" xml:space="preserve"> TEXT(AVERAGE(E14:E18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E14:E18),"0.0000")</f>
+        <v>0.9614±0.0048</v>
       </c>
       <c r="F19" t="str">
-        <f t="shared" ref="F19:K19" si="2" xml:space="preserve"> TEXT(AVERAGE(F14:F18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F14:F18),"0.0000")</f>
-        <v>0.9614±0.0048</v>
+        <f t="shared" si="2"/>
+        <v>0.9615±0.0048</v>
       </c>
       <c r="G19" t="str">
         <f t="shared" si="2"/>
-        <v>0.9615±0.0048</v>
+        <v>0.9297±0.0236</v>
       </c>
       <c r="H19" t="str">
         <f t="shared" si="2"/>
-        <v>0.9297±0.0236</v>
+        <v>0.8836±0.0304</v>
       </c>
       <c r="I19" t="str">
         <f t="shared" si="2"/>
-        <v>0.8836±0.0304</v>
+        <v>0.9261±0.0026</v>
       </c>
       <c r="J19" t="str">
         <f t="shared" si="2"/>
-        <v>0.9261±0.0026</v>
-      </c>
-      <c r="K19" t="str">
-        <f t="shared" si="2"/>
         <v>0.9054±0.0055</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A20" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C20" s="1">
         <v>42</v>
       </c>
       <c r="D20" s="4">
-        <v>30</v>
+        <v>0.98660000000000003</v>
       </c>
       <c r="E20" s="4">
-        <v>0.98660000000000003</v>
+        <v>0.96889999999999998</v>
       </c>
       <c r="F20" s="4">
-        <v>0.96889999999999998</v>
+        <v>0.96919999999999995</v>
       </c>
       <c r="G20" s="4">
-        <v>0.96919999999999995</v>
+        <v>0.9123</v>
       </c>
       <c r="H20" s="4">
-        <v>0.9123</v>
+        <v>0.92859999999999998</v>
       </c>
       <c r="I20" s="4">
-        <v>0.92859999999999998</v>
+        <v>0.9587</v>
       </c>
       <c r="J20" s="4">
-        <v>0.9587</v>
-      </c>
-      <c r="K20" s="4">
         <v>0.92030000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A21" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C21" s="1">
         <v>1234</v>
       </c>
       <c r="D21" s="4">
-        <v>28</v>
+        <v>0.95940000000000003</v>
       </c>
       <c r="E21" s="4">
-        <v>0.95940000000000003</v>
+        <v>0.91269999999999996</v>
       </c>
       <c r="F21" s="4">
-        <v>0.91269999999999996</v>
+        <v>0.91369999999999996</v>
       </c>
       <c r="G21" s="4">
-        <v>0.91369999999999996</v>
+        <v>0.90739999999999998</v>
       </c>
       <c r="H21" s="4">
-        <v>0.90739999999999998</v>
+        <v>0.875</v>
       </c>
       <c r="I21" s="4">
-        <v>0.875</v>
+        <v>0.94499999999999995</v>
       </c>
       <c r="J21" s="4">
-        <v>0.94499999999999995</v>
-      </c>
-      <c r="K21" s="4">
         <v>0.89090000000000003</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A22" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C22" s="1">
         <v>2025</v>
       </c>
       <c r="D22" s="4">
-        <v>21</v>
+        <v>0.97270000000000001</v>
       </c>
       <c r="E22" s="4">
-        <v>0.97270000000000001</v>
+        <v>0.92830000000000001</v>
       </c>
       <c r="F22" s="4">
-        <v>0.92830000000000001</v>
+        <v>0.92949999999999999</v>
       </c>
       <c r="G22" s="4">
-        <v>0.92949999999999999</v>
+        <v>0.90569999999999995</v>
       </c>
       <c r="H22" s="4">
-        <v>0.90569999999999995</v>
+        <v>0.85709999999999997</v>
       </c>
       <c r="I22" s="4">
-        <v>0.85709999999999997</v>
+        <v>0.94040000000000001</v>
       </c>
       <c r="J22" s="4">
-        <v>0.94040000000000001</v>
-      </c>
-      <c r="K22" s="4">
         <v>0.88070000000000004</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A23" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C23" s="1">
         <v>12345</v>
       </c>
       <c r="D23" s="4">
-        <v>21</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="E23" s="4">
-        <v>0.97799999999999998</v>
+        <v>0.94810000000000005</v>
       </c>
       <c r="F23" s="4">
-        <v>0.94810000000000005</v>
+        <v>0.9486</v>
       </c>
       <c r="G23" s="4">
-        <v>0.9486</v>
+        <v>0.89829999999999999</v>
       </c>
       <c r="H23" s="4">
-        <v>0.89829999999999999</v>
+        <v>0.94640000000000002</v>
       </c>
       <c r="I23" s="4">
-        <v>0.94640000000000002</v>
+        <v>0.9587</v>
       </c>
       <c r="J23" s="4">
-        <v>0.9587</v>
-      </c>
-      <c r="K23" s="4">
         <v>0.92169999999999996</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A24" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24" s="1">
         <v>666</v>
       </c>
       <c r="D24" s="4">
-        <v>18</v>
+        <v>0.98060000000000003</v>
       </c>
       <c r="E24" s="4">
-        <v>0.98060000000000003</v>
+        <v>0.94920000000000004</v>
       </c>
       <c r="F24" s="4">
-        <v>0.94920000000000004</v>
+        <v>0.94989999999999997</v>
       </c>
       <c r="G24" s="4">
-        <v>0.94989999999999997</v>
+        <v>0.9123</v>
       </c>
       <c r="H24" s="4">
-        <v>0.9123</v>
+        <v>0.92859999999999998</v>
       </c>
       <c r="I24" s="4">
-        <v>0.92859999999999998</v>
+        <v>0.9587</v>
       </c>
       <c r="J24" s="4">
-        <v>0.9587</v>
-      </c>
-      <c r="K24" s="4">
         <v>0.92030000000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
+      <c r="D25" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D20:D24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D20:D24),"0.0000")</f>
+        <v>0.9755±0.0103</v>
+      </c>
       <c r="E25" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E20:E24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E20:E24),"0.0000")</f>
-        <v>0.9755±0.0103</v>
+        <f t="shared" ref="E25:J25" si="3" xml:space="preserve"> TEXT(AVERAGE(E20:E24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E20:E24),"0.0000")</f>
+        <v>0.9414±0.0215</v>
       </c>
       <c r="F25" t="str">
-        <f t="shared" ref="F25:K25" si="3" xml:space="preserve"> TEXT(AVERAGE(F20:F24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F20:F24),"0.0000")</f>
-        <v>0.9414±0.0215</v>
+        <f t="shared" si="3"/>
+        <v>0.9422±0.0212</v>
       </c>
       <c r="G25" t="str">
         <f t="shared" si="3"/>
-        <v>0.9422±0.0212</v>
+        <v>0.9072±0.0058</v>
       </c>
       <c r="H25" t="str">
         <f t="shared" si="3"/>
-        <v>0.9072±0.0058</v>
+        <v>0.9071±0.0387</v>
       </c>
       <c r="I25" t="str">
         <f t="shared" si="3"/>
-        <v>0.9071±0.0387</v>
+        <v>0.9523±0.0089</v>
       </c>
       <c r="J25" t="str">
         <f t="shared" si="3"/>
-        <v>0.9523±0.0089</v>
-      </c>
-      <c r="K25" t="str">
-        <f t="shared" si="3"/>
         <v>0.9068±0.0195</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A26" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1">
         <v>42</v>
       </c>
       <c r="D26" s="4">
-        <v>30</v>
+        <v>0.9849</v>
       </c>
       <c r="E26" s="4">
-        <v>0.9849</v>
+        <v>0.99050000000000005</v>
       </c>
       <c r="F26" s="4">
         <v>0.99050000000000005</v>
       </c>
       <c r="G26" s="4">
-        <v>0.99050000000000005</v>
+        <v>0.93630000000000002</v>
       </c>
       <c r="H26" s="4">
-        <v>0.93630000000000002</v>
+        <v>0.98450000000000004</v>
       </c>
       <c r="I26" s="4">
-        <v>0.98450000000000004</v>
+        <v>0.94950000000000001</v>
       </c>
       <c r="J26" s="4">
-        <v>0.94950000000000001</v>
-      </c>
-      <c r="K26" s="4">
         <v>0.95979999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A27" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C27" s="1">
         <v>1234</v>
       </c>
       <c r="D27" s="4">
-        <v>19</v>
+        <v>0.97989999999999999</v>
       </c>
       <c r="E27" s="4">
-        <v>0.97989999999999999</v>
+        <v>0.98640000000000005</v>
       </c>
       <c r="F27" s="4">
-        <v>0.98640000000000005</v>
+        <v>0.98650000000000004</v>
       </c>
       <c r="G27" s="4">
-        <v>0.98650000000000004</v>
+        <v>0.94469999999999998</v>
       </c>
       <c r="H27" s="4">
-        <v>0.94469999999999998</v>
+        <v>0.96909999999999996</v>
       </c>
       <c r="I27" s="4">
-        <v>0.96909999999999996</v>
+        <v>0.94640000000000002</v>
       </c>
       <c r="J27" s="4">
-        <v>0.94640000000000002</v>
-      </c>
-      <c r="K27" s="4">
         <v>0.95669999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A28" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C28" s="1">
         <v>2025</v>
       </c>
       <c r="D28" s="4">
-        <v>30</v>
+        <v>0.98180000000000001</v>
       </c>
       <c r="E28" s="4">
-        <v>0.98180000000000001</v>
+        <v>0.98829999999999996</v>
       </c>
       <c r="F28" s="4">
-        <v>0.98829999999999996</v>
+        <v>0.98839999999999995</v>
       </c>
       <c r="G28" s="4">
-        <v>0.98839999999999995</v>
+        <v>0.95209999999999995</v>
       </c>
       <c r="H28" s="4">
-        <v>0.95209999999999995</v>
+        <v>0.92269999999999996</v>
       </c>
       <c r="I28" s="4">
-        <v>0.92269999999999996</v>
+        <v>0.92430000000000001</v>
       </c>
       <c r="J28" s="4">
-        <v>0.92430000000000001</v>
-      </c>
-      <c r="K28" s="4">
         <v>0.93720000000000003</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A29" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C29" s="1">
         <v>12345</v>
       </c>
       <c r="D29" s="4">
-        <v>24</v>
+        <v>0.98640000000000005</v>
       </c>
       <c r="E29" s="4">
-        <v>0.98640000000000005</v>
+        <v>0.99099999999999999</v>
       </c>
       <c r="F29" s="4">
-        <v>0.99099999999999999</v>
+        <v>0.99109999999999998</v>
       </c>
       <c r="G29" s="4">
-        <v>0.99109999999999998</v>
+        <v>0.96350000000000002</v>
       </c>
       <c r="H29" s="4">
-        <v>0.96350000000000002</v>
+        <v>0.9536</v>
       </c>
       <c r="I29" s="4">
-        <v>0.9536</v>
+        <v>0.94950000000000001</v>
       </c>
       <c r="J29" s="4">
-        <v>0.94950000000000001</v>
-      </c>
-      <c r="K29" s="4">
         <v>0.95850000000000002</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A30" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C30" s="1">
         <v>666</v>
       </c>
       <c r="D30" s="4">
-        <v>30</v>
+        <v>0.98480000000000001</v>
       </c>
       <c r="E30" s="4">
-        <v>0.98480000000000001</v>
+        <v>0.99009999999999998</v>
       </c>
       <c r="F30" s="4">
         <v>0.99009999999999998</v>
       </c>
       <c r="G30" s="4">
-        <v>0.99009999999999998</v>
+        <v>0.95679999999999998</v>
       </c>
       <c r="H30" s="4">
-        <v>0.95679999999999998</v>
+        <v>0.91239999999999999</v>
       </c>
       <c r="I30" s="4">
-        <v>0.91239999999999999</v>
+        <v>0.92110000000000003</v>
       </c>
       <c r="J30" s="4">
-        <v>0.92110000000000003</v>
-      </c>
-      <c r="K30" s="4">
         <v>0.93400000000000005</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="D31" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D26:D30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D26:D30),"0.0000")</f>
+        <v>0.9836±0.0026</v>
+      </c>
       <c r="E31" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E26:E30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E26:E30),"0.0000")</f>
-        <v>0.9836±0.0026</v>
+        <f t="shared" ref="E31:J31" si="4" xml:space="preserve"> TEXT(AVERAGE(E26:E30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E26:E30),"0.0000")</f>
+        <v>0.9893±0.0019</v>
       </c>
       <c r="F31" t="str">
-        <f t="shared" ref="F31:K31" si="4" xml:space="preserve"> TEXT(AVERAGE(F26:F30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F26:F30),"0.0000")</f>
+        <f t="shared" si="4"/>
         <v>0.9893±0.0019</v>
       </c>
       <c r="G31" t="str">
         <f t="shared" si="4"/>
-        <v>0.9893±0.0019</v>
+        <v>0.9507±0.0106</v>
       </c>
       <c r="H31" t="str">
         <f t="shared" si="4"/>
-        <v>0.9507±0.0106</v>
+        <v>0.9485±0.0305</v>
       </c>
       <c r="I31" t="str">
         <f t="shared" si="4"/>
-        <v>0.9485±0.0305</v>
+        <v>0.9382±0.0142</v>
       </c>
       <c r="J31" t="str">
-        <f t="shared" si="4"/>
-        <v>0.9382±0.0142</v>
-      </c>
-      <c r="K31" t="str">
         <f t="shared" si="4"/>
         <v>0.9492±0.0126</v>
       </c>
@@ -3699,186 +3532,168 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1">
         <v>42</v>
       </c>
       <c r="D2" s="4">
-        <v>11</v>
+        <v>0.88949999999999996</v>
       </c>
       <c r="E2" s="4">
-        <v>0.88949999999999996</v>
+        <v>0.87450000000000006</v>
       </c>
       <c r="F2" s="4">
-        <v>0.87450000000000006</v>
+        <v>0.87470000000000003</v>
       </c>
       <c r="G2" s="4">
-        <v>0.87470000000000003</v>
+        <v>0.75690000000000002</v>
       </c>
       <c r="H2" s="4">
-        <v>0.75690000000000002</v>
+        <v>0.86839999999999995</v>
       </c>
       <c r="I2" s="4">
-        <v>0.86839999999999995</v>
+        <v>0.80500000000000005</v>
       </c>
       <c r="J2" s="4">
-        <v>0.80500000000000005</v>
-      </c>
-      <c r="K2" s="4">
         <v>0.80879999999999996</v>
       </c>
       <c r="L2" s="4"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1">
         <v>1234</v>
       </c>
       <c r="D3" s="4">
-        <v>22</v>
+        <v>0.89580000000000004</v>
       </c>
       <c r="E3" s="4">
-        <v>0.89580000000000004</v>
+        <v>0.87580000000000002</v>
       </c>
       <c r="F3" s="4">
-        <v>0.87580000000000002</v>
+        <v>0.876</v>
       </c>
       <c r="G3" s="4">
-        <v>0.876</v>
+        <v>0.82289999999999996</v>
       </c>
       <c r="H3" s="4">
-        <v>0.82289999999999996</v>
+        <v>0.79469999999999996</v>
       </c>
       <c r="I3" s="4">
-        <v>0.79469999999999996</v>
+        <v>0.82130000000000003</v>
       </c>
       <c r="J3" s="4">
-        <v>0.82130000000000003</v>
-      </c>
-      <c r="K3" s="4">
         <v>0.80859999999999999</v>
       </c>
       <c r="L3" s="4"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1">
         <v>2025</v>
       </c>
       <c r="D4" s="4">
-        <v>15</v>
+        <v>0.88780000000000003</v>
       </c>
       <c r="E4" s="4">
-        <v>0.88780000000000003</v>
+        <v>0.86729999999999996</v>
       </c>
       <c r="F4" s="4">
-        <v>0.86729999999999996</v>
+        <v>0.86760000000000004</v>
       </c>
       <c r="G4" s="4">
-        <v>0.86760000000000004</v>
+        <v>0.81559999999999999</v>
       </c>
       <c r="H4" s="4">
-        <v>0.81559999999999999</v>
+        <v>0.76839999999999997</v>
       </c>
       <c r="I4" s="4">
-        <v>0.76839999999999997</v>
+        <v>0.8075</v>
       </c>
       <c r="J4" s="4">
-        <v>0.8075</v>
-      </c>
-      <c r="K4" s="4">
         <v>0.7913</v>
       </c>
       <c r="L4" s="4"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1">
         <v>12345</v>
       </c>
       <c r="D5" s="4">
-        <v>13</v>
+        <v>0.88970000000000005</v>
       </c>
       <c r="E5" s="4">
-        <v>0.88970000000000005</v>
+        <v>0.87690000000000001</v>
       </c>
       <c r="F5" s="4">
-        <v>0.87690000000000001</v>
+        <v>0.87719999999999998</v>
       </c>
       <c r="G5" s="4">
-        <v>0.87719999999999998</v>
+        <v>0.77270000000000005</v>
       </c>
       <c r="H5" s="4">
-        <v>0.77270000000000005</v>
+        <v>0.85</v>
       </c>
       <c r="I5" s="4">
-        <v>0.85</v>
+        <v>0.81</v>
       </c>
       <c r="J5" s="4">
-        <v>0.81</v>
-      </c>
-      <c r="K5" s="4">
         <v>0.8095</v>
       </c>
       <c r="L5" s="4"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" s="1">
         <v>666</v>
       </c>
       <c r="D6" s="4">
-        <v>10</v>
+        <v>0.89270000000000005</v>
       </c>
       <c r="E6" s="4">
-        <v>0.89270000000000005</v>
+        <v>0.87370000000000003</v>
       </c>
       <c r="F6" s="4">
-        <v>0.87370000000000003</v>
+        <v>0.874</v>
       </c>
       <c r="G6" s="4">
-        <v>0.874</v>
+        <v>0.81940000000000002</v>
       </c>
       <c r="H6" s="4">
-        <v>0.81940000000000002</v>
+        <v>0.77629999999999999</v>
       </c>
       <c r="I6" s="4">
-        <v>0.77629999999999999</v>
+        <v>0.8125</v>
       </c>
       <c r="J6" s="4">
-        <v>0.8125</v>
-      </c>
-      <c r="K6" s="4">
         <v>0.79730000000000001</v>
       </c>
       <c r="L6" s="4"/>
@@ -3887,212 +3702,196 @@
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
+      <c r="D7" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D2:D6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D2:D6),"0.0000")</f>
+        <v>0.8911±0.0032</v>
+      </c>
       <c r="E7" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E2:E6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E2:E6),"0.0000")</f>
-        <v>0.8911±0.0032</v>
+        <f t="shared" ref="E7:J7" si="0" xml:space="preserve"> TEXT(AVERAGE(E2:E6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E2:E6),"0.0000")</f>
+        <v>0.8736±0.0037</v>
       </c>
       <c r="F7" t="str">
-        <f t="shared" ref="F7:K7" si="0" xml:space="preserve"> TEXT(AVERAGE(F2:F6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F2:F6),"0.0000")</f>
-        <v>0.8736±0.0037</v>
+        <f t="shared" si="0"/>
+        <v>0.8739±0.0037</v>
       </c>
       <c r="G7" t="str">
         <f t="shared" si="0"/>
-        <v>0.8739±0.0037</v>
+        <v>0.7975±0.0305</v>
       </c>
       <c r="H7" t="str">
         <f t="shared" si="0"/>
-        <v>0.7975±0.0305</v>
+        <v>0.8116±0.0450</v>
       </c>
       <c r="I7" t="str">
         <f t="shared" si="0"/>
-        <v>0.8116±0.0450</v>
+        <v>0.8113±0.0063</v>
       </c>
       <c r="J7" t="str">
         <f t="shared" si="0"/>
-        <v>0.8113±0.0063</v>
-      </c>
-      <c r="K7" t="str">
-        <f t="shared" si="0"/>
         <v>0.8031±0.0083</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A8" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1">
         <v>42</v>
       </c>
       <c r="D8" s="4">
-        <v>17</v>
+        <v>0.86060000000000003</v>
       </c>
       <c r="E8" s="4">
-        <v>0.86060000000000003</v>
+        <v>0.86140000000000005</v>
       </c>
       <c r="F8" s="4">
-        <v>0.86140000000000005</v>
+        <v>0.86160000000000003</v>
       </c>
       <c r="G8" s="4">
-        <v>0.86160000000000003</v>
+        <v>0.7177</v>
       </c>
       <c r="H8" s="4">
-        <v>0.7177</v>
+        <v>0.84860000000000002</v>
       </c>
       <c r="I8" s="4">
-        <v>0.84860000000000002</v>
+        <v>0.75929999999999997</v>
       </c>
       <c r="J8" s="4">
-        <v>0.75929999999999997</v>
-      </c>
-      <c r="K8" s="4">
         <v>0.77769999999999995</v>
       </c>
       <c r="L8" s="4"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A9" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1">
         <v>1234</v>
       </c>
       <c r="D9" s="4">
-        <v>10</v>
+        <v>0.86799999999999999</v>
       </c>
       <c r="E9" s="4">
-        <v>0.86799999999999999</v>
+        <v>0.87480000000000002</v>
       </c>
       <c r="F9" s="4">
-        <v>0.87480000000000002</v>
+        <v>0.87490000000000001</v>
       </c>
       <c r="G9" s="4">
-        <v>0.87490000000000001</v>
+        <v>0.79900000000000004</v>
       </c>
       <c r="H9" s="4">
-        <v>0.79900000000000004</v>
+        <v>0.77710000000000001</v>
       </c>
       <c r="I9" s="4">
-        <v>0.77710000000000001</v>
+        <v>0.79239999999999999</v>
       </c>
       <c r="J9" s="4">
-        <v>0.79239999999999999</v>
-      </c>
-      <c r="K9" s="4">
         <v>0.78790000000000004</v>
       </c>
       <c r="L9" s="4"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A10" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="1">
         <v>2025</v>
       </c>
       <c r="D10" s="4">
-        <v>14</v>
+        <v>0.86839999999999995</v>
       </c>
       <c r="E10" s="4">
-        <v>0.86839999999999995</v>
+        <v>0.87309999999999999</v>
       </c>
       <c r="F10" s="4">
-        <v>0.87309999999999999</v>
+        <v>0.87319999999999998</v>
       </c>
       <c r="G10" s="4">
-        <v>0.87319999999999998</v>
+        <v>0.74760000000000004</v>
       </c>
       <c r="H10" s="4">
-        <v>0.74760000000000004</v>
+        <v>0.81879999999999997</v>
       </c>
       <c r="I10" s="4">
-        <v>0.81879999999999997</v>
+        <v>0.77290000000000003</v>
       </c>
       <c r="J10" s="4">
-        <v>0.77290000000000003</v>
-      </c>
-      <c r="K10" s="4">
         <v>0.78159999999999996</v>
       </c>
       <c r="L10" s="4"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A11" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="1">
         <v>12345</v>
       </c>
       <c r="D11" s="4">
-        <v>21</v>
+        <v>0.86809999999999998</v>
       </c>
       <c r="E11" s="4">
-        <v>0.86809999999999998</v>
+        <v>0.875</v>
       </c>
       <c r="F11" s="4">
-        <v>0.875</v>
+        <v>0.87509999999999999</v>
       </c>
       <c r="G11" s="4">
-        <v>0.87509999999999999</v>
+        <v>0.78010000000000002</v>
       </c>
       <c r="H11" s="4">
-        <v>0.78010000000000002</v>
+        <v>0.80330000000000001</v>
       </c>
       <c r="I11" s="4">
-        <v>0.80330000000000001</v>
+        <v>0.79010000000000002</v>
       </c>
       <c r="J11" s="4">
-        <v>0.79010000000000002</v>
-      </c>
-      <c r="K11" s="4">
         <v>0.79149999999999998</v>
       </c>
       <c r="L11" s="4"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" s="1">
         <v>666</v>
       </c>
       <c r="D12" s="4">
-        <v>14</v>
+        <v>0.87229999999999996</v>
       </c>
       <c r="E12" s="4">
-        <v>0.87229999999999996</v>
+        <v>0.87480000000000002</v>
       </c>
       <c r="F12" s="4">
-        <v>0.87480000000000002</v>
+        <v>0.875</v>
       </c>
       <c r="G12" s="4">
-        <v>0.875</v>
+        <v>0.68430000000000002</v>
       </c>
       <c r="H12" s="4">
-        <v>0.68430000000000002</v>
+        <v>0.87839999999999996</v>
       </c>
       <c r="I12" s="4">
-        <v>0.87839999999999996</v>
+        <v>0.73860000000000003</v>
       </c>
       <c r="J12" s="4">
-        <v>0.73860000000000003</v>
-      </c>
-      <c r="K12" s="4">
         <v>0.76929999999999998</v>
       </c>
       <c r="L12" s="4"/>
@@ -4101,212 +3900,196 @@
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+      <c r="D13" t="str">
+        <f t="shared" ref="D13:J13" si="1" xml:space="preserve"> TEXT(AVERAGE(D8:D12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D8:D12),"0.0000")</f>
+        <v>0.8675±0.0042</v>
+      </c>
       <c r="E13" t="str">
-        <f t="shared" ref="E13:K13" si="1" xml:space="preserve"> TEXT(AVERAGE(E8:E12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E8:E12),"0.0000")</f>
-        <v>0.8675±0.0042</v>
+        <f t="shared" si="1"/>
+        <v>0.8718±0.0059</v>
       </c>
       <c r="F13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8718±0.0059</v>
+        <v>0.8720±0.0058</v>
       </c>
       <c r="G13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8720±0.0058</v>
+        <v>0.7457±0.0463</v>
       </c>
       <c r="H13" t="str">
         <f t="shared" si="1"/>
-        <v>0.7457±0.0463</v>
+        <v>0.8252±0.0394</v>
       </c>
       <c r="I13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8252±0.0394</v>
+        <v>0.7707±0.0224</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="1"/>
-        <v>0.7707±0.0224</v>
-      </c>
-      <c r="K13" t="str">
-        <f t="shared" si="1"/>
         <v>0.7816±0.0087</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A14" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C14" s="1">
         <v>42</v>
       </c>
       <c r="D14" s="4">
-        <v>29</v>
+        <v>0.72929999999999995</v>
       </c>
       <c r="E14" s="4">
-        <v>0.72929999999999995</v>
+        <v>0.75439999999999996</v>
       </c>
       <c r="F14" s="4">
-        <v>0.75439999999999996</v>
+        <v>0.75480000000000003</v>
       </c>
       <c r="G14" s="4">
-        <v>0.75480000000000003</v>
+        <v>0.7026</v>
       </c>
       <c r="H14" s="4">
-        <v>0.7026</v>
+        <v>0.77890000000000004</v>
       </c>
       <c r="I14" s="4">
-        <v>0.77890000000000004</v>
+        <v>0.68059999999999998</v>
       </c>
       <c r="J14" s="4">
-        <v>0.68059999999999998</v>
-      </c>
-      <c r="K14" s="4">
         <v>0.73880000000000001</v>
       </c>
       <c r="L14" s="4"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A15" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" s="1">
         <v>1234</v>
       </c>
       <c r="D15" s="4">
-        <v>10</v>
+        <v>0.74060000000000004</v>
       </c>
       <c r="E15" s="4">
-        <v>0.74060000000000004</v>
+        <v>0.7591</v>
       </c>
       <c r="F15" s="4">
-        <v>0.7591</v>
+        <v>0.75960000000000005</v>
       </c>
       <c r="G15" s="4">
-        <v>0.75960000000000005</v>
+        <v>0.73440000000000005</v>
       </c>
       <c r="H15" s="4">
-        <v>0.73440000000000005</v>
+        <v>0.68510000000000004</v>
       </c>
       <c r="I15" s="4">
-        <v>0.68510000000000004</v>
+        <v>0.67369999999999997</v>
       </c>
       <c r="J15" s="4">
-        <v>0.67369999999999997</v>
-      </c>
-      <c r="K15" s="4">
         <v>0.70889999999999997</v>
       </c>
       <c r="L15" s="4"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A16" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C16" s="1">
         <v>2025</v>
       </c>
       <c r="D16" s="4">
-        <v>20</v>
+        <v>0.7611</v>
       </c>
       <c r="E16" s="4">
-        <v>0.7611</v>
+        <v>0.77200000000000002</v>
       </c>
       <c r="F16" s="4">
-        <v>0.77200000000000002</v>
+        <v>0.77239999999999998</v>
       </c>
       <c r="G16" s="4">
-        <v>0.77239999999999998</v>
+        <v>0.74109999999999998</v>
       </c>
       <c r="H16" s="4">
-        <v>0.74109999999999998</v>
+        <v>0.77690000000000003</v>
       </c>
       <c r="I16" s="4">
-        <v>0.77690000000000003</v>
+        <v>0.71319999999999995</v>
       </c>
       <c r="J16" s="4">
-        <v>0.71319999999999995</v>
-      </c>
-      <c r="K16" s="4">
         <v>0.75849999999999995</v>
       </c>
       <c r="L16" s="4"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A17" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C17" s="1">
         <v>12345</v>
       </c>
       <c r="D17" s="4">
-        <v>12</v>
+        <v>0.74560000000000004</v>
       </c>
       <c r="E17" s="4">
-        <v>0.74560000000000004</v>
+        <v>0.76049999999999995</v>
       </c>
       <c r="F17" s="4">
-        <v>0.76049999999999995</v>
+        <v>0.76090000000000002</v>
       </c>
       <c r="G17" s="4">
-        <v>0.76090000000000002</v>
+        <v>0.74970000000000003</v>
       </c>
       <c r="H17" s="4">
-        <v>0.74970000000000003</v>
+        <v>0.70089999999999997</v>
       </c>
       <c r="I17" s="4">
-        <v>0.70089999999999997</v>
+        <v>0.69089999999999996</v>
       </c>
       <c r="J17" s="4">
-        <v>0.69089999999999996</v>
-      </c>
-      <c r="K17" s="4">
         <v>0.72450000000000003</v>
       </c>
       <c r="L17" s="4"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A18" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C18" s="1">
         <v>666</v>
       </c>
       <c r="D18" s="4">
-        <v>14</v>
+        <v>0.7712</v>
       </c>
       <c r="E18" s="4">
-        <v>0.7712</v>
+        <v>0.77549999999999997</v>
       </c>
       <c r="F18" s="4">
-        <v>0.77549999999999997</v>
+        <v>0.77639999999999998</v>
       </c>
       <c r="G18" s="4">
-        <v>0.77639999999999998</v>
+        <v>0.72170000000000001</v>
       </c>
       <c r="H18" s="4">
-        <v>0.72170000000000001</v>
+        <v>0.86280000000000001</v>
       </c>
       <c r="I18" s="4">
-        <v>0.86280000000000001</v>
+        <v>0.72750000000000004</v>
       </c>
       <c r="J18" s="4">
-        <v>0.72750000000000004</v>
-      </c>
-      <c r="K18" s="4">
         <v>0.78600000000000003</v>
       </c>
       <c r="L18" s="4"/>
@@ -4315,212 +4098,196 @@
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
+      <c r="D19" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D14:D18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D14:D18),"0.0000")</f>
+        <v>0.7496±0.0166</v>
+      </c>
       <c r="E19" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E14:E18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E14:E18),"0.0000")</f>
-        <v>0.7496±0.0166</v>
+        <f t="shared" ref="E19:J19" si="2" xml:space="preserve"> TEXT(AVERAGE(E14:E18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E14:E18),"0.0000")</f>
+        <v>0.7643±0.0090</v>
       </c>
       <c r="F19" t="str">
-        <f t="shared" ref="F19:K19" si="2" xml:space="preserve"> TEXT(AVERAGE(F14:F18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F14:F18),"0.0000")</f>
-        <v>0.7643±0.0090</v>
+        <f t="shared" si="2"/>
+        <v>0.7648±0.0091</v>
       </c>
       <c r="G19" t="str">
         <f t="shared" si="2"/>
-        <v>0.7648±0.0091</v>
+        <v>0.7299±0.0184</v>
       </c>
       <c r="H19" t="str">
         <f t="shared" si="2"/>
-        <v>0.7299±0.0184</v>
+        <v>0.7609±0.0713</v>
       </c>
       <c r="I19" t="str">
         <f t="shared" si="2"/>
-        <v>0.7609±0.0713</v>
+        <v>0.6972±0.0226</v>
       </c>
       <c r="J19" t="str">
         <f t="shared" si="2"/>
-        <v>0.6972±0.0226</v>
-      </c>
-      <c r="K19" t="str">
-        <f t="shared" si="2"/>
         <v>0.7433±0.0300</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A20" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C20" s="1">
         <v>42</v>
       </c>
       <c r="D20" s="4">
-        <v>26</v>
+        <v>0.86990000000000001</v>
       </c>
       <c r="E20" s="4">
-        <v>0.86990000000000001</v>
+        <v>0.85199999999999998</v>
       </c>
       <c r="F20" s="4">
-        <v>0.85199999999999998</v>
+        <v>0.8528</v>
       </c>
       <c r="G20" s="4">
-        <v>0.8528</v>
+        <v>0.76429999999999998</v>
       </c>
       <c r="H20" s="4">
-        <v>0.76429999999999998</v>
+        <v>0.81079999999999997</v>
       </c>
       <c r="I20" s="4">
-        <v>0.81079999999999997</v>
+        <v>0.81100000000000005</v>
       </c>
       <c r="J20" s="4">
-        <v>0.81100000000000005</v>
-      </c>
-      <c r="K20" s="4">
         <v>0.78690000000000004</v>
       </c>
       <c r="L20" s="4"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A21" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C21" s="1">
         <v>1234</v>
       </c>
       <c r="D21" s="4">
-        <v>25</v>
+        <v>0.87139999999999995</v>
       </c>
       <c r="E21" s="4">
-        <v>0.87139999999999995</v>
+        <v>0.86799999999999999</v>
       </c>
       <c r="F21" s="4">
-        <v>0.86799999999999999</v>
+        <v>0.86839999999999995</v>
       </c>
       <c r="G21" s="4">
-        <v>0.86839999999999995</v>
+        <v>0.78</v>
       </c>
       <c r="H21" s="4">
-        <v>0.78</v>
+        <v>0.79049999999999998</v>
       </c>
       <c r="I21" s="4">
-        <v>0.79049999999999998</v>
+        <v>0.81399999999999995</v>
       </c>
       <c r="J21" s="4">
-        <v>0.81399999999999995</v>
-      </c>
-      <c r="K21" s="4">
         <v>0.78520000000000001</v>
       </c>
       <c r="L21" s="4"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A22" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C22" s="1">
         <v>2025</v>
       </c>
       <c r="D22" s="4">
-        <v>22</v>
+        <v>0.87229999999999996</v>
       </c>
       <c r="E22" s="4">
-        <v>0.87229999999999996</v>
+        <v>0.86070000000000002</v>
       </c>
       <c r="F22" s="4">
-        <v>0.86070000000000002</v>
+        <v>0.86129999999999995</v>
       </c>
       <c r="G22" s="4">
-        <v>0.86129999999999995</v>
+        <v>0.79720000000000002</v>
       </c>
       <c r="H22" s="4">
-        <v>0.79720000000000002</v>
+        <v>0.77029999999999998</v>
       </c>
       <c r="I22" s="4">
-        <v>0.77029999999999998</v>
+        <v>0.81689999999999996</v>
       </c>
       <c r="J22" s="4">
-        <v>0.81689999999999996</v>
-      </c>
-      <c r="K22" s="4">
         <v>0.78349999999999997</v>
       </c>
       <c r="L22" s="4"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A23" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C23" s="1">
         <v>12345</v>
       </c>
       <c r="D23" s="4">
-        <v>13</v>
+        <v>0.87029999999999996</v>
       </c>
       <c r="E23" s="4">
-        <v>0.87029999999999996</v>
+        <v>0.8548</v>
       </c>
       <c r="F23" s="4">
-        <v>0.8548</v>
+        <v>0.85540000000000005</v>
       </c>
       <c r="G23" s="4">
-        <v>0.85540000000000005</v>
+        <v>0.72670000000000001</v>
       </c>
       <c r="H23" s="4">
-        <v>0.72670000000000001</v>
+        <v>0.79049999999999998</v>
       </c>
       <c r="I23" s="4">
-        <v>0.79049999999999998</v>
+        <v>0.78200000000000003</v>
       </c>
       <c r="J23" s="4">
-        <v>0.78200000000000003</v>
-      </c>
-      <c r="K23" s="4">
         <v>0.75729999999999997</v>
       </c>
       <c r="L23" s="4"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A24" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24" s="1">
         <v>666</v>
       </c>
       <c r="D24" s="4">
-        <v>10</v>
+        <v>0.84970000000000001</v>
       </c>
       <c r="E24" s="4">
-        <v>0.84970000000000001</v>
+        <v>0.80289999999999995</v>
       </c>
       <c r="F24" s="4">
-        <v>0.80289999999999995</v>
+        <v>0.80530000000000002</v>
       </c>
       <c r="G24" s="4">
-        <v>0.80530000000000002</v>
+        <v>0.78380000000000005</v>
       </c>
       <c r="H24" s="4">
         <v>0.78380000000000005</v>
       </c>
       <c r="I24" s="4">
-        <v>0.78380000000000005</v>
+        <v>0.81399999999999995</v>
       </c>
       <c r="J24" s="4">
-        <v>0.81399999999999995</v>
-      </c>
-      <c r="K24" s="4">
         <v>0.78380000000000005</v>
       </c>
       <c r="L24" s="4"/>
@@ -4529,242 +4296,226 @@
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
+      <c r="D25" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D20:D24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D20:D24),"0.0000")</f>
+        <v>0.8667±0.0096</v>
+      </c>
       <c r="E25" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E20:E24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E20:E24),"0.0000")</f>
-        <v>0.8667±0.0096</v>
+        <f t="shared" ref="E25:J25" si="3" xml:space="preserve"> TEXT(AVERAGE(E20:E24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E20:E24),"0.0000")</f>
+        <v>0.8477±0.0258</v>
       </c>
       <c r="F25" t="str">
-        <f t="shared" ref="F25:K25" si="3" xml:space="preserve"> TEXT(AVERAGE(F20:F24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F20:F24),"0.0000")</f>
-        <v>0.8477±0.0258</v>
+        <f t="shared" si="3"/>
+        <v>0.8486±0.0250</v>
       </c>
       <c r="G25" t="str">
         <f t="shared" si="3"/>
-        <v>0.8486±0.0250</v>
+        <v>0.7704±0.0271</v>
       </c>
       <c r="H25" t="str">
         <f t="shared" si="3"/>
-        <v>0.7704±0.0271</v>
+        <v>0.7892±0.0146</v>
       </c>
       <c r="I25" t="str">
         <f t="shared" si="3"/>
-        <v>0.7892±0.0146</v>
+        <v>0.8076±0.0145</v>
       </c>
       <c r="J25" t="str">
         <f t="shared" si="3"/>
-        <v>0.8076±0.0145</v>
-      </c>
-      <c r="K25" t="str">
-        <f t="shared" si="3"/>
         <v>0.7793±0.0124</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A26" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1">
         <v>42</v>
       </c>
       <c r="D26" s="4">
-        <v>29</v>
+        <v>0.75560000000000005</v>
       </c>
       <c r="E26" s="4">
-        <v>0.75560000000000005</v>
+        <v>0.73819999999999997</v>
       </c>
       <c r="F26" s="4">
-        <v>0.73819999999999997</v>
+        <v>0.74029999999999996</v>
       </c>
       <c r="G26" s="4">
-        <v>0.74029999999999996</v>
+        <v>0.74550000000000005</v>
       </c>
       <c r="H26" s="4">
-        <v>0.74550000000000005</v>
+        <v>0.67210000000000003</v>
       </c>
       <c r="I26" s="4">
-        <v>0.67210000000000003</v>
+        <v>0.70689999999999997</v>
       </c>
       <c r="J26" s="4">
         <v>0.70689999999999997</v>
       </c>
-      <c r="K26" s="4">
-        <v>0.70689999999999997</v>
-      </c>
       <c r="L26" s="4"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A27" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C27" s="1">
         <v>1234</v>
       </c>
       <c r="D27" s="4">
-        <v>6</v>
+        <v>0.75880000000000003</v>
       </c>
       <c r="E27" s="4">
-        <v>0.75880000000000003</v>
+        <v>0.74850000000000005</v>
       </c>
       <c r="F27" s="4">
-        <v>0.74850000000000005</v>
+        <v>0.751</v>
       </c>
       <c r="G27" s="4">
-        <v>0.751</v>
+        <v>0.622</v>
       </c>
       <c r="H27" s="4">
-        <v>0.622</v>
+        <v>0.83609999999999995</v>
       </c>
       <c r="I27" s="4">
-        <v>0.83609999999999995</v>
+        <v>0.64659999999999995</v>
       </c>
       <c r="J27" s="4">
-        <v>0.64659999999999995</v>
-      </c>
-      <c r="K27" s="4">
         <v>0.71330000000000005</v>
       </c>
       <c r="L27" s="4"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A28" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C28" s="1">
         <v>2025</v>
       </c>
       <c r="D28" s="4">
-        <v>13</v>
+        <v>0.76539999999999997</v>
       </c>
       <c r="E28" s="4">
-        <v>0.76539999999999997</v>
+        <v>0.75</v>
       </c>
       <c r="F28" s="4">
-        <v>0.75</v>
+        <v>0.75560000000000005</v>
       </c>
       <c r="G28" s="4">
-        <v>0.75560000000000005</v>
+        <v>0.64670000000000005</v>
       </c>
       <c r="H28" s="4">
-        <v>0.64670000000000005</v>
+        <v>0.88519999999999999</v>
       </c>
       <c r="I28" s="4">
-        <v>0.88519999999999999</v>
+        <v>0.68530000000000002</v>
       </c>
       <c r="J28" s="4">
-        <v>0.68530000000000002</v>
-      </c>
-      <c r="K28" s="4">
         <v>0.74739999999999995</v>
       </c>
       <c r="L28" s="4"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A29" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C29" s="1">
         <v>12345</v>
       </c>
       <c r="D29" s="4">
-        <v>6</v>
+        <v>0.76700000000000002</v>
       </c>
       <c r="E29" s="4">
-        <v>0.76700000000000002</v>
+        <v>0.75349999999999995</v>
       </c>
       <c r="F29" s="4">
-        <v>0.75349999999999995</v>
+        <v>0.75600000000000001</v>
       </c>
       <c r="G29" s="4">
-        <v>0.75600000000000001</v>
+        <v>0.68530000000000002</v>
       </c>
       <c r="H29" s="4">
-        <v>0.68530000000000002</v>
+        <v>0.80330000000000001</v>
       </c>
       <c r="I29" s="4">
-        <v>0.80330000000000001</v>
+        <v>0.7026</v>
       </c>
       <c r="J29" s="4">
-        <v>0.7026</v>
-      </c>
-      <c r="K29" s="4">
         <v>0.73960000000000004</v>
       </c>
       <c r="L29" s="4"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A30" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C30" s="1">
         <v>666</v>
       </c>
       <c r="D30" s="4">
-        <v>15</v>
+        <v>0.75309999999999999</v>
       </c>
       <c r="E30" s="4">
-        <v>0.75309999999999999</v>
+        <v>0.75149999999999995</v>
       </c>
       <c r="F30" s="4">
-        <v>0.75149999999999995</v>
+        <v>0.75339999999999996</v>
       </c>
       <c r="G30" s="4">
-        <v>0.75339999999999996</v>
+        <v>0.69110000000000005</v>
       </c>
       <c r="H30" s="4">
-        <v>0.69110000000000005</v>
+        <v>0.69669999999999999</v>
       </c>
       <c r="I30" s="4">
-        <v>0.69669999999999999</v>
+        <v>0.67669999999999997</v>
       </c>
       <c r="J30" s="4">
-        <v>0.67669999999999997</v>
-      </c>
-      <c r="K30" s="4">
         <v>0.69389999999999996</v>
       </c>
       <c r="L30" s="4"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="D31" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D26:D30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D26:D30),"0.0000")</f>
+        <v>0.7600±0.0061</v>
+      </c>
       <c r="E31" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E26:E30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E26:E30),"0.0000")</f>
-        <v>0.7600±0.0061</v>
+        <f t="shared" ref="E31:J31" si="4" xml:space="preserve"> TEXT(AVERAGE(E26:E30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E26:E30),"0.0000")</f>
+        <v>0.7483±0.0060</v>
       </c>
       <c r="F31" t="str">
-        <f t="shared" ref="F31:K31" si="4" xml:space="preserve"> TEXT(AVERAGE(F26:F30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F26:F30),"0.0000")</f>
-        <v>0.7483±0.0060</v>
+        <f t="shared" si="4"/>
+        <v>0.7513±0.0064</v>
       </c>
       <c r="G31" t="str">
         <f t="shared" si="4"/>
-        <v>0.7513±0.0064</v>
+        <v>0.6781±0.0472</v>
       </c>
       <c r="H31" t="str">
         <f t="shared" si="4"/>
-        <v>0.6781±0.0472</v>
+        <v>0.7787±0.0913</v>
       </c>
       <c r="I31" t="str">
         <f t="shared" si="4"/>
-        <v>0.7787±0.0913</v>
+        <v>0.6836±0.0241</v>
       </c>
       <c r="J31" t="str">
-        <f t="shared" si="4"/>
-        <v>0.6836±0.0241</v>
-      </c>
-      <c r="K31" t="str">
         <f t="shared" si="4"/>
         <v>0.7202±0.0225</v>
       </c>
@@ -4778,10 +4529,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45275180-57AC-4BB6-B1CC-6E162588BEA5}">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4812,1047 +4563,965 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1">
         <v>42</v>
       </c>
       <c r="D2" s="4">
-        <v>30</v>
+        <v>0.95299999999999996</v>
       </c>
       <c r="E2" s="4">
-        <v>0.95299999999999996</v>
+        <v>0.94269999999999998</v>
       </c>
       <c r="F2" s="4">
         <v>0.94269999999999998</v>
       </c>
       <c r="G2" s="4">
-        <v>0.94269999999999998</v>
+        <v>0.91910000000000003</v>
       </c>
       <c r="H2" s="4">
-        <v>0.91910000000000003</v>
+        <v>0.87129999999999996</v>
       </c>
       <c r="I2" s="4">
-        <v>0.87129999999999996</v>
+        <v>0.90249999999999997</v>
       </c>
       <c r="J2" s="4">
-        <v>0.90249999999999997</v>
-      </c>
-      <c r="K2" s="4">
         <v>0.89449999999999996</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1">
         <v>1234</v>
       </c>
       <c r="D3" s="4">
-        <v>19</v>
+        <v>0.95789999999999997</v>
       </c>
       <c r="E3" s="4">
-        <v>0.95789999999999997</v>
+        <v>0.95569999999999999</v>
       </c>
       <c r="F3" s="4">
-        <v>0.95569999999999999</v>
+        <v>0.95579999999999998</v>
       </c>
       <c r="G3" s="4">
-        <v>0.95579999999999998</v>
+        <v>0.87409999999999999</v>
       </c>
       <c r="H3" s="4">
-        <v>0.87409999999999999</v>
+        <v>0.89359999999999995</v>
       </c>
       <c r="I3" s="4">
-        <v>0.89359999999999995</v>
+        <v>0.88839999999999997</v>
       </c>
       <c r="J3" s="4">
-        <v>0.88839999999999997</v>
-      </c>
-      <c r="K3" s="4">
         <v>0.88370000000000004</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1">
         <v>2025</v>
       </c>
       <c r="D4" s="4">
+        <v>0.95630000000000004</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0.94740000000000002</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0.94750000000000001</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0.85429999999999995</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.94310000000000005</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.89659999999999995</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.89649999999999996</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="E4" s="4">
-        <v>0.95630000000000004</v>
-      </c>
-      <c r="F4" s="4">
-        <v>0.94740000000000002</v>
-      </c>
-      <c r="G4" s="4">
-        <v>0.94750000000000001</v>
-      </c>
-      <c r="H4" s="4">
-        <v>0.85429999999999995</v>
-      </c>
-      <c r="I4" s="4">
-        <v>0.94310000000000005</v>
-      </c>
-      <c r="J4" s="4">
-        <v>0.89659999999999995</v>
-      </c>
-      <c r="K4" s="4">
-        <v>0.89649999999999996</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="C5" s="1">
         <v>12345</v>
       </c>
       <c r="D5" s="4">
-        <v>22</v>
+        <v>0.95830000000000004</v>
       </c>
       <c r="E5" s="4">
-        <v>0.95830000000000004</v>
+        <v>0.95079999999999998</v>
       </c>
       <c r="F5" s="4">
-        <v>0.95079999999999998</v>
+        <v>0.95089999999999997</v>
       </c>
       <c r="G5" s="4">
-        <v>0.95089999999999997</v>
+        <v>0.86739999999999995</v>
       </c>
       <c r="H5" s="4">
-        <v>0.86739999999999995</v>
+        <v>0.92330000000000001</v>
       </c>
       <c r="I5" s="4">
-        <v>0.92330000000000001</v>
+        <v>0.89659999999999995</v>
       </c>
       <c r="J5" s="4">
-        <v>0.89659999999999995</v>
-      </c>
-      <c r="K5" s="4">
         <v>0.89449999999999996</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" s="1">
         <v>666</v>
       </c>
       <c r="D6" s="4">
-        <v>28</v>
+        <v>0.95799999999999996</v>
       </c>
       <c r="E6" s="4">
-        <v>0.95799999999999996</v>
+        <v>0.95230000000000004</v>
       </c>
       <c r="F6" s="4">
-        <v>0.95230000000000004</v>
+        <v>0.95240000000000002</v>
       </c>
       <c r="G6" s="4">
-        <v>0.95240000000000002</v>
+        <v>0.8921</v>
       </c>
       <c r="H6" s="4">
-        <v>0.8921</v>
+        <v>0.92079999999999995</v>
       </c>
       <c r="I6" s="4">
-        <v>0.92079999999999995</v>
+        <v>0.90949999999999998</v>
       </c>
       <c r="J6" s="4">
-        <v>0.90949999999999998</v>
-      </c>
-      <c r="K6" s="4">
         <v>0.90620000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
+      <c r="D7" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D2:D6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D2:D6),"0.0000")</f>
+        <v>0.9567±0.0022</v>
+      </c>
       <c r="E7" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E2:E6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E2:E6),"0.0000")</f>
-        <v>0.9567±0.0022</v>
+        <f t="shared" ref="E7:J7" si="0" xml:space="preserve"> TEXT(AVERAGE(E2:E6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E2:E6),"0.0000")</f>
+        <v>0.9498±0.0050</v>
       </c>
       <c r="F7" t="str">
-        <f t="shared" ref="F7:K7" si="0" xml:space="preserve"> TEXT(AVERAGE(F2:F6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F2:F6),"0.0000")</f>
-        <v>0.9498±0.0050</v>
+        <f t="shared" si="0"/>
+        <v>0.9499±0.0050</v>
       </c>
       <c r="G7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9499±0.0050</v>
+        <v>0.8814±0.0251</v>
       </c>
       <c r="H7" t="str">
         <f t="shared" si="0"/>
-        <v>0.8814±0.0251</v>
+        <v>0.9104±0.0281</v>
       </c>
       <c r="I7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9104±0.0281</v>
+        <v>0.8987±0.0078</v>
       </c>
       <c r="J7" t="str">
         <f t="shared" si="0"/>
-        <v>0.8987±0.0078</v>
-      </c>
-      <c r="K7" t="str">
-        <f t="shared" si="0"/>
         <v>0.8951±0.0080</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1">
         <v>42</v>
       </c>
       <c r="D8" s="4">
-        <v>23</v>
+        <v>0.94989999999999997</v>
       </c>
       <c r="E8" s="4">
+        <v>0.94979999999999998</v>
+      </c>
+      <c r="F8" s="4">
         <v>0.94989999999999997</v>
       </c>
-      <c r="F8" s="4">
-        <v>0.94979999999999998</v>
-      </c>
       <c r="G8" s="4">
-        <v>0.94989999999999997</v>
+        <v>0.86460000000000004</v>
       </c>
       <c r="H8" s="4">
-        <v>0.86460000000000004</v>
+        <v>0.89329999999999998</v>
       </c>
       <c r="I8" s="4">
-        <v>0.89329999999999998</v>
+        <v>0.87809999999999999</v>
       </c>
       <c r="J8" s="4">
-        <v>0.87809999999999999</v>
-      </c>
-      <c r="K8" s="4">
         <v>0.87870000000000004</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1">
         <v>1234</v>
       </c>
       <c r="D9" s="4">
-        <v>19</v>
+        <v>0.94550000000000001</v>
       </c>
       <c r="E9" s="4">
-        <v>0.94550000000000001</v>
+        <v>0.94489999999999996</v>
       </c>
       <c r="F9" s="4">
-        <v>0.94489999999999996</v>
+        <v>0.94499999999999995</v>
       </c>
       <c r="G9" s="4">
-        <v>0.94499999999999995</v>
+        <v>0.90610000000000002</v>
       </c>
       <c r="H9" s="4">
-        <v>0.90610000000000002</v>
+        <v>0.84060000000000001</v>
       </c>
       <c r="I9" s="4">
-        <v>0.84060000000000001</v>
+        <v>0.87809999999999999</v>
       </c>
       <c r="J9" s="4">
-        <v>0.87809999999999999</v>
-      </c>
-      <c r="K9" s="4">
         <v>0.87209999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="1">
         <v>2025</v>
       </c>
       <c r="D10" s="4">
-        <v>22</v>
+        <v>0.94720000000000004</v>
       </c>
       <c r="E10" s="4">
-        <v>0.94720000000000004</v>
+        <v>0.94630000000000003</v>
       </c>
       <c r="F10" s="4">
         <v>0.94630000000000003</v>
       </c>
       <c r="G10" s="4">
-        <v>0.94630000000000003</v>
+        <v>0.8407</v>
       </c>
       <c r="H10" s="4">
-        <v>0.8407</v>
+        <v>0.91400000000000003</v>
       </c>
       <c r="I10" s="4">
-        <v>0.91400000000000003</v>
+        <v>0.87190000000000001</v>
       </c>
       <c r="J10" s="4">
-        <v>0.87190000000000001</v>
-      </c>
-      <c r="K10" s="4">
         <v>0.87580000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A11" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="1">
         <v>12345</v>
       </c>
       <c r="D11" s="4">
-        <v>29</v>
+        <v>0.94850000000000001</v>
       </c>
       <c r="E11" s="4">
         <v>0.94850000000000001</v>
       </c>
       <c r="F11" s="4">
-        <v>0.94850000000000001</v>
+        <v>0.9486</v>
       </c>
       <c r="G11" s="4">
-        <v>0.9486</v>
+        <v>0.85560000000000003</v>
       </c>
       <c r="H11" s="4">
-        <v>0.85560000000000003</v>
+        <v>0.90369999999999995</v>
       </c>
       <c r="I11" s="4">
-        <v>0.90369999999999995</v>
+        <v>0.877</v>
       </c>
       <c r="J11" s="4">
-        <v>0.877</v>
-      </c>
-      <c r="K11" s="4">
         <v>0.879</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" s="1">
         <v>666</v>
       </c>
       <c r="D12" s="4">
-        <v>10</v>
+        <v>0.94610000000000005</v>
       </c>
       <c r="E12" s="4">
-        <v>0.94610000000000005</v>
+        <v>0.94620000000000004</v>
       </c>
       <c r="F12" s="4">
         <v>0.94620000000000004</v>
       </c>
       <c r="G12" s="4">
-        <v>0.94620000000000004</v>
+        <v>0.84240000000000004</v>
       </c>
       <c r="H12" s="4">
-        <v>0.84240000000000004</v>
+        <v>0.90710000000000002</v>
       </c>
       <c r="I12" s="4">
-        <v>0.90710000000000002</v>
+        <v>0.87019999999999997</v>
       </c>
       <c r="J12" s="4">
-        <v>0.87019999999999997</v>
-      </c>
-      <c r="K12" s="4">
         <v>0.87350000000000005</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+      <c r="D13" t="str">
+        <f t="shared" ref="D13:J13" si="1" xml:space="preserve"> TEXT(AVERAGE(D8:D12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D8:D12),"0.0000")</f>
+        <v>0.9474±0.0018</v>
+      </c>
       <c r="E13" t="str">
-        <f t="shared" ref="E13:K13" si="1" xml:space="preserve"> TEXT(AVERAGE(E8:E12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E8:E12),"0.0000")</f>
-        <v>0.9474±0.0018</v>
+        <f t="shared" si="1"/>
+        <v>0.9471±0.0020</v>
       </c>
       <c r="F13" t="str">
         <f t="shared" si="1"/>
-        <v>0.9471±0.0020</v>
+        <v>0.9472±0.0020</v>
       </c>
       <c r="G13" t="str">
         <f t="shared" si="1"/>
-        <v>0.9472±0.0020</v>
+        <v>0.8619±0.0266</v>
       </c>
       <c r="H13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8619±0.0266</v>
+        <v>0.8917±0.0295</v>
       </c>
       <c r="I13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8917±0.0295</v>
+        <v>0.8751±0.0037</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8751±0.0037</v>
-      </c>
-      <c r="K13" t="str">
-        <f t="shared" si="1"/>
         <v>0.8758±0.0031</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C14" s="1">
         <v>42</v>
       </c>
       <c r="D14" s="4">
-        <v>8</v>
+        <v>0.77690000000000003</v>
       </c>
       <c r="E14" s="4">
-        <v>0.77690000000000003</v>
+        <v>0.78859999999999997</v>
       </c>
       <c r="F14" s="4">
-        <v>0.78859999999999997</v>
+        <v>0.78890000000000005</v>
       </c>
       <c r="G14" s="4">
-        <v>0.78890000000000005</v>
+        <v>0.60029999999999994</v>
       </c>
       <c r="H14" s="4">
-        <v>0.60029999999999994</v>
+        <v>0.97019999999999995</v>
       </c>
       <c r="I14" s="4">
-        <v>0.97019999999999995</v>
+        <v>0.62829999999999997</v>
       </c>
       <c r="J14" s="4">
-        <v>0.62829999999999997</v>
-      </c>
-      <c r="K14" s="4">
         <v>0.74170000000000003</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A15" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" s="1">
         <v>1234</v>
       </c>
       <c r="D15" s="4">
-        <v>10</v>
+        <v>0.75990000000000002</v>
       </c>
       <c r="E15" s="4">
-        <v>0.75990000000000002</v>
+        <v>0.7903</v>
       </c>
       <c r="F15" s="4">
-        <v>0.7903</v>
+        <v>0.79049999999999998</v>
       </c>
       <c r="G15" s="4">
-        <v>0.79049999999999998</v>
+        <v>0.62360000000000004</v>
       </c>
       <c r="H15" s="4">
-        <v>0.62360000000000004</v>
+        <v>0.90329999999999999</v>
       </c>
       <c r="I15" s="4">
-        <v>0.90329999999999999</v>
+        <v>0.64700000000000002</v>
       </c>
       <c r="J15" s="4">
-        <v>0.64700000000000002</v>
-      </c>
-      <c r="K15" s="4">
         <v>0.73780000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A16" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C16" s="1">
         <v>2025</v>
       </c>
       <c r="D16" s="4">
+        <v>0.72140000000000004</v>
+      </c>
+      <c r="E16" s="4">
+        <v>0.74609999999999999</v>
+      </c>
+      <c r="F16" s="4">
+        <v>0.74629999999999996</v>
+      </c>
+      <c r="G16" s="4">
+        <v>0.6139</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.9224</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.63819999999999999</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.73719999999999997</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="E16" s="4">
-        <v>0.72140000000000004</v>
-      </c>
-      <c r="F16" s="4">
-        <v>0.74609999999999999</v>
-      </c>
-      <c r="G16" s="4">
-        <v>0.74629999999999996</v>
-      </c>
-      <c r="H16" s="4">
-        <v>0.6139</v>
-      </c>
-      <c r="I16" s="4">
-        <v>0.9224</v>
-      </c>
-      <c r="J16" s="4">
-        <v>0.63819999999999999</v>
-      </c>
-      <c r="K16" s="4">
-        <v>0.73719999999999997</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A17" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="C17" s="1">
         <v>12345</v>
       </c>
       <c r="D17" s="4">
-        <v>5</v>
+        <v>0.78639999999999999</v>
       </c>
       <c r="E17" s="4">
-        <v>0.78639999999999999</v>
+        <v>0.80800000000000005</v>
       </c>
       <c r="F17" s="4">
-        <v>0.80800000000000005</v>
+        <v>0.80820000000000003</v>
       </c>
       <c r="G17" s="4">
-        <v>0.80820000000000003</v>
+        <v>0.61240000000000006</v>
       </c>
       <c r="H17" s="4">
-        <v>0.61240000000000006</v>
+        <v>0.94689999999999996</v>
       </c>
       <c r="I17" s="4">
-        <v>0.94689999999999996</v>
+        <v>0.6411</v>
       </c>
       <c r="J17" s="4">
-        <v>0.6411</v>
-      </c>
-      <c r="K17" s="4">
         <v>0.74370000000000003</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A18" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C18" s="1">
         <v>666</v>
       </c>
       <c r="D18" s="4">
-        <v>9</v>
+        <v>0.72099999999999997</v>
       </c>
       <c r="E18" s="4">
-        <v>0.72099999999999997</v>
+        <v>0.74660000000000004</v>
       </c>
       <c r="F18" s="4">
-        <v>0.74660000000000004</v>
+        <v>0.74690000000000001</v>
       </c>
       <c r="G18" s="4">
-        <v>0.74690000000000001</v>
+        <v>0.62009999999999998</v>
       </c>
       <c r="H18" s="4">
-        <v>0.62009999999999998</v>
+        <v>0.90010000000000001</v>
       </c>
       <c r="I18" s="4">
-        <v>0.90010000000000001</v>
+        <v>0.64170000000000005</v>
       </c>
       <c r="J18" s="4">
-        <v>0.64170000000000005</v>
-      </c>
-      <c r="K18" s="4">
         <v>0.73429999999999995</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
+      <c r="D19" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D14:D18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D14:D18),"0.0000")</f>
+        <v>0.7531±0.0306</v>
+      </c>
       <c r="E19" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E14:E18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E14:E18),"0.0000")</f>
-        <v>0.7531±0.0306</v>
+        <f t="shared" ref="E19:J19" si="2" xml:space="preserve"> TEXT(AVERAGE(E14:E18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E14:E18),"0.0000")</f>
+        <v>0.7759±0.0280</v>
       </c>
       <c r="F19" t="str">
-        <f t="shared" ref="F19:K19" si="2" xml:space="preserve"> TEXT(AVERAGE(F14:F18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F14:F18),"0.0000")</f>
-        <v>0.7759±0.0280</v>
+        <f t="shared" si="2"/>
+        <v>0.7762±0.0280</v>
       </c>
       <c r="G19" t="str">
         <f t="shared" si="2"/>
-        <v>0.7762±0.0280</v>
+        <v>0.6141±0.0089</v>
       </c>
       <c r="H19" t="str">
         <f t="shared" si="2"/>
-        <v>0.6141±0.0089</v>
+        <v>0.9286±0.0298</v>
       </c>
       <c r="I19" t="str">
         <f t="shared" si="2"/>
-        <v>0.9286±0.0298</v>
+        <v>0.6393±0.0069</v>
       </c>
       <c r="J19" t="str">
         <f t="shared" si="2"/>
-        <v>0.6393±0.0069</v>
-      </c>
-      <c r="K19" t="str">
-        <f t="shared" si="2"/>
         <v>0.7389±0.0037</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A20" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C20" s="1">
         <v>42</v>
       </c>
       <c r="D20" s="4">
-        <v>12</v>
+        <v>0.95840000000000003</v>
       </c>
       <c r="E20" s="4">
-        <v>0.95840000000000003</v>
+        <v>0.96179999999999999</v>
       </c>
       <c r="F20" s="4">
-        <v>0.96179999999999999</v>
+        <v>0.96189999999999998</v>
       </c>
       <c r="G20" s="4">
-        <v>0.96189999999999998</v>
+        <v>0.91359999999999997</v>
       </c>
       <c r="H20" s="4">
-        <v>0.91359999999999997</v>
+        <v>0.87770000000000004</v>
       </c>
       <c r="I20" s="4">
-        <v>0.87770000000000004</v>
+        <v>0.89870000000000005</v>
       </c>
       <c r="J20" s="4">
-        <v>0.89870000000000005</v>
-      </c>
-      <c r="K20" s="4">
         <v>0.89529999999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A21" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C21" s="1">
         <v>1234</v>
       </c>
       <c r="D21" s="4">
-        <v>15</v>
+        <v>0.96150000000000002</v>
       </c>
       <c r="E21" s="4">
-        <v>0.96150000000000002</v>
+        <v>0.96330000000000005</v>
       </c>
       <c r="F21" s="4">
-        <v>0.96330000000000005</v>
+        <v>0.96340000000000003</v>
       </c>
       <c r="G21" s="4">
-        <v>0.96340000000000003</v>
+        <v>0.90869999999999995</v>
       </c>
       <c r="H21" s="4">
-        <v>0.90869999999999995</v>
+        <v>0.86899999999999999</v>
       </c>
       <c r="I21" s="4">
-        <v>0.86899999999999999</v>
+        <v>0.89219999999999999</v>
       </c>
       <c r="J21" s="4">
-        <v>0.89219999999999999</v>
-      </c>
-      <c r="K21" s="4">
         <v>0.88839999999999997</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A22" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C22" s="1">
         <v>2025</v>
       </c>
       <c r="D22" s="4">
-        <v>9</v>
+        <v>0.96630000000000005</v>
       </c>
       <c r="E22" s="4">
-        <v>0.96630000000000005</v>
+        <v>0.96860000000000002</v>
       </c>
       <c r="F22" s="4">
-        <v>0.96860000000000002</v>
+        <v>0.96870000000000001</v>
       </c>
       <c r="G22" s="4">
-        <v>0.96870000000000001</v>
+        <v>0.92859999999999998</v>
       </c>
       <c r="H22" s="4">
-        <v>0.92859999999999998</v>
+        <v>0.85150000000000003</v>
       </c>
       <c r="I22" s="4">
-        <v>0.85150000000000003</v>
+        <v>0.89439999999999997</v>
       </c>
       <c r="J22" s="4">
-        <v>0.89439999999999997</v>
-      </c>
-      <c r="K22" s="4">
         <v>0.88839999999999997</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A23" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C23" s="1">
         <v>12345</v>
       </c>
       <c r="D23" s="4">
-        <v>23</v>
+        <v>0.96730000000000005</v>
       </c>
       <c r="E23" s="4">
-        <v>0.96730000000000005</v>
+        <v>0.9667</v>
       </c>
       <c r="F23" s="4">
-        <v>0.9667</v>
+        <v>0.96679999999999999</v>
       </c>
       <c r="G23" s="4">
-        <v>0.96679999999999999</v>
+        <v>0.8851</v>
       </c>
       <c r="H23" s="4">
-        <v>0.8851</v>
+        <v>0.9083</v>
       </c>
       <c r="I23" s="4">
-        <v>0.9083</v>
+        <v>0.89659999999999995</v>
       </c>
       <c r="J23" s="4">
-        <v>0.89659999999999995</v>
-      </c>
-      <c r="K23" s="4">
         <v>0.89649999999999996</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A24" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24" s="1">
         <v>666</v>
       </c>
       <c r="D24" s="4">
-        <v>18</v>
+        <v>0.96599999999999997</v>
       </c>
       <c r="E24" s="4">
-        <v>0.96599999999999997</v>
+        <v>0.96870000000000001</v>
       </c>
       <c r="F24" s="4">
         <v>0.96870000000000001</v>
       </c>
       <c r="G24" s="4">
-        <v>0.96870000000000001</v>
+        <v>0.91669999999999996</v>
       </c>
       <c r="H24" s="4">
-        <v>0.91669999999999996</v>
+        <v>0.91269999999999996</v>
       </c>
       <c r="I24" s="4">
-        <v>0.91269999999999996</v>
+        <v>0.91590000000000005</v>
       </c>
       <c r="J24" s="4">
-        <v>0.91590000000000005</v>
-      </c>
-      <c r="K24" s="4">
         <v>0.91469999999999996</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
+      <c r="D25" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D20:D24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D20:D24),"0.0000")</f>
+        <v>0.9639±0.0038</v>
+      </c>
       <c r="E25" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E20:E24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E20:E24),"0.0000")</f>
-        <v>0.9639±0.0038</v>
+        <f t="shared" ref="E25:J25" si="3" xml:space="preserve"> TEXT(AVERAGE(E20:E24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E20:E24),"0.0000")</f>
+        <v>0.9658±0.0031</v>
       </c>
       <c r="F25" t="str">
-        <f t="shared" ref="F25:K25" si="3" xml:space="preserve"> TEXT(AVERAGE(F20:F24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F20:F24),"0.0000")</f>
-        <v>0.9658±0.0031</v>
+        <f t="shared" si="3"/>
+        <v>0.9659±0.0031</v>
       </c>
       <c r="G25" t="str">
         <f t="shared" si="3"/>
-        <v>0.9659±0.0031</v>
+        <v>0.9105±0.0160</v>
       </c>
       <c r="H25" t="str">
         <f t="shared" si="3"/>
-        <v>0.9105±0.0160</v>
+        <v>0.8838±0.0261</v>
       </c>
       <c r="I25" t="str">
         <f t="shared" si="3"/>
-        <v>0.8838±0.0261</v>
+        <v>0.8996±0.0095</v>
       </c>
       <c r="J25" t="str">
         <f t="shared" si="3"/>
-        <v>0.8996±0.0095</v>
-      </c>
-      <c r="K25" t="str">
-        <f t="shared" si="3"/>
         <v>0.8967±0.0108</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A26" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1">
         <v>42</v>
       </c>
       <c r="D26" s="4">
-        <v>26</v>
+        <v>0.83220000000000005</v>
       </c>
       <c r="E26" s="4">
-        <v>0.83220000000000005</v>
+        <v>0.88929999999999998</v>
       </c>
       <c r="F26" s="4">
-        <v>0.88929999999999998</v>
+        <v>0.88990000000000002</v>
       </c>
       <c r="G26" s="4">
-        <v>0.88990000000000002</v>
+        <v>0.79169999999999996</v>
       </c>
       <c r="H26" s="4">
         <v>0.79169999999999996</v>
       </c>
       <c r="I26" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="J26" s="4">
         <v>0.79169999999999996</v>
       </c>
-      <c r="J26" s="4">
-        <v>0.75</v>
-      </c>
-      <c r="K26" s="4">
-        <v>0.79169999999999996</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A27" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C27" s="1">
         <v>1234</v>
       </c>
       <c r="D27" s="4">
-        <v>5</v>
+        <v>0.81279999999999997</v>
       </c>
       <c r="E27" s="4">
-        <v>0.81279999999999997</v>
+        <v>0.86480000000000001</v>
       </c>
       <c r="F27" s="4">
-        <v>0.86480000000000001</v>
+        <v>0.86599999999999999</v>
       </c>
       <c r="G27" s="4">
-        <v>0.86599999999999999</v>
+        <v>0.73040000000000005</v>
       </c>
       <c r="H27" s="4">
-        <v>0.73040000000000005</v>
+        <v>0.875</v>
       </c>
       <c r="I27" s="4">
-        <v>0.875</v>
+        <v>0.73119999999999996</v>
       </c>
       <c r="J27" s="4">
-        <v>0.73119999999999996</v>
-      </c>
-      <c r="K27" s="4">
         <v>0.79620000000000002</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A28" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C28" s="1">
         <v>2025</v>
       </c>
       <c r="D28" s="4">
-        <v>29</v>
+        <v>0.80500000000000005</v>
       </c>
       <c r="E28" s="4">
-        <v>0.80500000000000005</v>
+        <v>0.84460000000000002</v>
       </c>
       <c r="F28" s="4">
-        <v>0.84460000000000002</v>
+        <v>0.8458</v>
       </c>
       <c r="G28" s="4">
-        <v>0.8458</v>
+        <v>0.76790000000000003</v>
       </c>
       <c r="H28" s="4">
-        <v>0.76790000000000003</v>
+        <v>0.89580000000000004</v>
       </c>
       <c r="I28" s="4">
-        <v>0.89580000000000004</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="J28" s="4">
-        <v>0.77500000000000002</v>
-      </c>
-      <c r="K28" s="4">
         <v>0.82689999999999997</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A29" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C29" s="1">
         <v>12345</v>
       </c>
       <c r="D29" s="4">
-        <v>5</v>
+        <v>0.82550000000000001</v>
       </c>
       <c r="E29" s="4">
-        <v>0.82550000000000001</v>
+        <v>0.86970000000000003</v>
       </c>
       <c r="F29" s="4">
-        <v>0.86970000000000003</v>
+        <v>0.87060000000000004</v>
       </c>
       <c r="G29" s="4">
-        <v>0.87060000000000004</v>
+        <v>0.76419999999999999</v>
       </c>
       <c r="H29" s="4">
-        <v>0.76419999999999999</v>
+        <v>0.84379999999999999</v>
       </c>
       <c r="I29" s="4">
-        <v>0.84379999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="J29" s="4">
-        <v>0.75</v>
-      </c>
-      <c r="K29" s="4">
         <v>0.80200000000000005</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A30" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C30" s="1">
         <v>666</v>
       </c>
       <c r="D30" s="4">
-        <v>22</v>
+        <v>0.8115</v>
       </c>
       <c r="E30" s="4">
-        <v>0.8115</v>
+        <v>0.86739999999999995</v>
       </c>
       <c r="F30" s="4">
-        <v>0.86739999999999995</v>
+        <v>0.86829999999999996</v>
       </c>
       <c r="G30" s="4">
-        <v>0.86829999999999996</v>
+        <v>0.77139999999999997</v>
       </c>
       <c r="H30" s="4">
-        <v>0.77139999999999997</v>
+        <v>0.84379999999999999</v>
       </c>
       <c r="I30" s="4">
-        <v>0.84379999999999999</v>
+        <v>0.75619999999999998</v>
       </c>
       <c r="J30" s="4">
-        <v>0.75619999999999998</v>
-      </c>
-      <c r="K30" s="4">
         <v>0.80600000000000005</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="D31" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D26:D30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D26:D30),"0.0000")</f>
+        <v>0.8174±0.0111</v>
+      </c>
       <c r="E31" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E26:E30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E26:E30),"0.0000")</f>
-        <v>0.8174±0.0111</v>
+        <f t="shared" ref="E31:J31" si="4" xml:space="preserve"> TEXT(AVERAGE(E26:E30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E26:E30),"0.0000")</f>
+        <v>0.8672±0.0159</v>
       </c>
       <c r="F31" t="str">
-        <f t="shared" ref="F31:K31" si="4" xml:space="preserve"> TEXT(AVERAGE(F26:F30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F26:F30),"0.0000")</f>
-        <v>0.8672±0.0159</v>
+        <f t="shared" si="4"/>
+        <v>0.8681±0.0157</v>
       </c>
       <c r="G31" t="str">
         <f t="shared" si="4"/>
-        <v>0.8681±0.0157</v>
+        <v>0.7651±0.0221</v>
       </c>
       <c r="H31" t="str">
         <f t="shared" si="4"/>
-        <v>0.7651±0.0221</v>
+        <v>0.8500±0.0394</v>
       </c>
       <c r="I31" t="str">
         <f t="shared" si="4"/>
-        <v>0.8500±0.0394</v>
+        <v>0.7525±0.0157</v>
       </c>
       <c r="J31" t="str">
-        <f t="shared" si="4"/>
-        <v>0.7525±0.0157</v>
-      </c>
-      <c r="K31" t="str">
         <f t="shared" si="4"/>
         <v>0.8046±0.0136</v>
       </c>
